--- a/research/traditional_assets/database/data/norway/norway_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_telecom_equipment.xlsx
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1531,22 +1531,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09657025643946254</v>
+        <v>0.09639290187529573</v>
       </c>
       <c r="C2">
-        <v>156.7934511361986</v>
+        <v>155.7385846496698</v>
       </c>
       <c r="D2">
-        <v>147.8334511361986</v>
+        <v>148.3516846496698</v>
       </c>
       <c r="E2">
-        <v>-2.01</v>
+        <v>-0.4368999999999996</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.5731</v>
       </c>
       <c r="G2">
         <v>8.960000000000001</v>
@@ -1567,28 +1567,28 @@
         <v>2.27</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07912693</v>
       </c>
       <c r="N2">
-        <v>2.27</v>
+        <v>2.19087307</v>
       </c>
       <c r="O2">
-        <v>0.4994</v>
+        <v>0.4819920754</v>
       </c>
       <c r="P2">
-        <v>1.7706</v>
+        <v>1.7088809946</v>
       </c>
       <c r="Q2">
-        <v>3.9506</v>
+        <v>3.8888809946</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09657025643946254</v>
+        <v>0.09697026452050073</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.181761305323342</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>28.68808381672333</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09639290187529573</v>
+        <v>0.0962155473111289</v>
       </c>
       <c r="C3">
-        <v>155.7385846496698</v>
+        <v>154.6873643034219</v>
       </c>
       <c r="D3">
-        <v>148.3516846496698</v>
+        <v>148.8735643034219</v>
       </c>
       <c r="E3">
-        <v>-0.4368999999999996</v>
+        <v>1.136200000000001</v>
       </c>
       <c r="F3">
-        <v>1.5731</v>
+        <v>3.1462</v>
       </c>
       <c r="G3">
         <v>8.960000000000001</v>
@@ -1649,28 +1649,28 @@
         <v>2.27</v>
       </c>
       <c r="M3">
-        <v>0.07912693</v>
+        <v>0.15825386</v>
       </c>
       <c r="N3">
-        <v>2.19087307</v>
+        <v>2.11174614</v>
       </c>
       <c r="O3">
-        <v>0.4819920754</v>
+        <v>0.4645841508</v>
       </c>
       <c r="P3">
-        <v>1.7088809946</v>
+        <v>1.6471619892</v>
       </c>
       <c r="Q3">
-        <v>3.8888809946</v>
+        <v>3.8271619892</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09697026452050073</v>
+        <v>0.09737843603176419</v>
       </c>
       <c r="T3">
-        <v>1.181761305323342</v>
+        <v>1.191187899116956</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>28.68808381672333</v>
+        <v>14.34404190836167</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1695,22 +1695,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0962155473111289</v>
+        <v>0.0961130727469621</v>
       </c>
       <c r="C4">
-        <v>154.6873643034219</v>
+        <v>153.4174807993548</v>
       </c>
       <c r="D4">
-        <v>148.8735643034219</v>
+        <v>149.1767807993548</v>
       </c>
       <c r="E4">
-        <v>1.136200000000001</v>
+        <v>2.7093</v>
       </c>
       <c r="F4">
-        <v>3.1462</v>
+        <v>4.7193</v>
       </c>
       <c r="G4">
         <v>8.960000000000001</v>
@@ -1731,45 +1731,45 @@
         <v>2.27</v>
       </c>
       <c r="M4">
-        <v>0.15825386</v>
+        <v>0.25248255</v>
       </c>
       <c r="N4">
-        <v>2.11174614</v>
+        <v>2.01751745</v>
       </c>
       <c r="O4">
-        <v>0.4645841508</v>
+        <v>0.443853839</v>
       </c>
       <c r="P4">
-        <v>1.6471619892</v>
+        <v>1.573663611</v>
       </c>
       <c r="Q4">
-        <v>3.8271619892</v>
+        <v>3.753663611</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09737843603176419</v>
+        <v>0.09779502345047639</v>
       </c>
       <c r="T4">
-        <v>1.191187899116956</v>
+        <v>1.2008088556692</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.039234</v>
+        <v>0.04173</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>14.34404190836167</v>
+        <v>8.990720348792422</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1777,22 +1777,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0961130727469621</v>
+        <v>0.09598563818279526</v>
       </c>
       <c r="C5">
-        <v>153.4174807993548</v>
+        <v>152.2231799684665</v>
       </c>
       <c r="D5">
-        <v>149.1767807993548</v>
+        <v>149.5555799684664</v>
       </c>
       <c r="E5">
-        <v>2.7093</v>
+        <v>4.282400000000001</v>
       </c>
       <c r="F5">
-        <v>4.7193</v>
+        <v>6.292400000000001</v>
       </c>
       <c r="G5">
         <v>8.960000000000001</v>
@@ -1813,45 +1813,45 @@
         <v>2.27</v>
       </c>
       <c r="M5">
-        <v>0.25248255</v>
+        <v>0.3416773200000001</v>
       </c>
       <c r="N5">
-        <v>2.01751745</v>
+        <v>1.92832268</v>
       </c>
       <c r="O5">
-        <v>0.443853839</v>
+        <v>0.4242309896</v>
       </c>
       <c r="P5">
-        <v>1.573663611</v>
+        <v>1.5040916904</v>
       </c>
       <c r="Q5">
-        <v>3.753663611</v>
+        <v>3.6840916904</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09779502345047639</v>
+        <v>0.09822028977374507</v>
       </c>
       <c r="T5">
-        <v>1.2008088556692</v>
+        <v>1.210630248816283</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.990720348792422</v>
+        <v>6.643695285364564</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1859,22 +1859,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09598563818279526</v>
+        <v>0.09587848361862845</v>
       </c>
       <c r="C6">
-        <v>152.2231799684665</v>
+        <v>150.9700889190624</v>
       </c>
       <c r="D6">
-        <v>149.5555799684664</v>
+        <v>149.8755889190624</v>
       </c>
       <c r="E6">
-        <v>4.282400000000001</v>
+        <v>5.855500000000001</v>
       </c>
       <c r="F6">
-        <v>6.292400000000001</v>
+        <v>7.865500000000001</v>
       </c>
       <c r="G6">
         <v>8.960000000000001</v>
@@ -1895,45 +1895,45 @@
         <v>2.27</v>
       </c>
       <c r="M6">
-        <v>0.3416773200000001</v>
+        <v>0.43496215</v>
       </c>
       <c r="N6">
-        <v>1.92832268</v>
+        <v>1.83503785</v>
       </c>
       <c r="O6">
-        <v>0.4242309896</v>
+        <v>0.403708327</v>
       </c>
       <c r="P6">
-        <v>1.5040916904</v>
+        <v>1.431329523</v>
       </c>
       <c r="Q6">
-        <v>3.6840916904</v>
+        <v>3.611329523</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09822028977374507</v>
+        <v>0.09865450907224048</v>
       </c>
       <c r="T6">
-        <v>1.210630248816283</v>
+        <v>1.220658408134884</v>
       </c>
       <c r="U6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.643695285364564</v>
+        <v>5.218844904091079</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09587848361862845</v>
+        <v>0.09585712905446163</v>
       </c>
       <c r="C7">
-        <v>150.9700889190624</v>
+        <v>149.4609264228919</v>
       </c>
       <c r="D7">
-        <v>149.8755889190624</v>
+        <v>149.9395264228919</v>
       </c>
       <c r="E7">
-        <v>5.855500000000001</v>
+        <v>7.428600000000001</v>
       </c>
       <c r="F7">
-        <v>7.865500000000001</v>
+        <v>9.438600000000001</v>
       </c>
       <c r="G7">
         <v>8.960000000000001</v>
@@ -1977,45 +1977,45 @@
         <v>2.27</v>
       </c>
       <c r="M7">
-        <v>0.43496215</v>
+        <v>0.5455510800000001</v>
       </c>
       <c r="N7">
-        <v>1.83503785</v>
+        <v>1.72444892</v>
       </c>
       <c r="O7">
-        <v>0.403708327</v>
+        <v>0.3793787624</v>
       </c>
       <c r="P7">
-        <v>1.431329523</v>
+        <v>1.3450701576</v>
       </c>
       <c r="Q7">
-        <v>3.611329523</v>
+        <v>3.5250701576</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09865450907224048</v>
+        <v>0.09909796707921451</v>
       </c>
       <c r="T7">
-        <v>1.220658408134884</v>
+        <v>1.23089993254537</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y7">
-        <v>5.218844904091079</v>
+        <v>4.160930265228326</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2023,22 +2023,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09585712905446163</v>
+        <v>0.0960822544902948</v>
       </c>
       <c r="C8">
-        <v>149.4609264228919</v>
+        <v>147.2165120282462</v>
       </c>
       <c r="D8">
-        <v>149.9395264228919</v>
+        <v>149.2682120282462</v>
       </c>
       <c r="E8">
-        <v>7.428599999999999</v>
+        <v>9.0017</v>
       </c>
       <c r="F8">
-        <v>9.438599999999999</v>
+        <v>11.0117</v>
       </c>
       <c r="G8">
         <v>8.960000000000001</v>
@@ -2059,45 +2059,45 @@
         <v>2.27</v>
       </c>
       <c r="M8">
-        <v>0.54555108</v>
+        <v>0.70584997</v>
       </c>
       <c r="N8">
-        <v>1.72444892</v>
+        <v>1.56415003</v>
       </c>
       <c r="O8">
-        <v>0.3793787624</v>
+        <v>0.3441130066</v>
       </c>
       <c r="P8">
-        <v>1.3450701576</v>
+        <v>1.2200370234</v>
       </c>
       <c r="Q8">
-        <v>3.5250701576</v>
+        <v>3.4000370234</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09909796707921451</v>
+        <v>0.09955096181752129</v>
       </c>
       <c r="T8">
-        <v>1.23089993254537</v>
+        <v>1.24136170479264</v>
       </c>
       <c r="U8">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.04508400000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.160930265228327</v>
+        <v>3.215980869135689</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09608225449029482</v>
+        <v>0.096499259926128</v>
       </c>
       <c r="C9">
-        <v>147.2165120282461</v>
+        <v>144.4156691400152</v>
       </c>
       <c r="D9">
-        <v>149.2682120282461</v>
+        <v>148.0404691400151</v>
       </c>
       <c r="E9">
-        <v>9.001700000000001</v>
+        <v>10.5748</v>
       </c>
       <c r="F9">
-        <v>11.0117</v>
+        <v>12.5848</v>
       </c>
       <c r="G9">
         <v>8.960000000000001</v>
@@ -2141,45 +2141,45 @@
         <v>2.27</v>
       </c>
       <c r="M9">
-        <v>0.7058499700000002</v>
+        <v>0.9048471200000001</v>
       </c>
       <c r="N9">
-        <v>1.56415003</v>
+        <v>1.36515288</v>
       </c>
       <c r="O9">
-        <v>0.3441130066</v>
+        <v>0.3003336336</v>
       </c>
       <c r="P9">
-        <v>1.2200370234</v>
+        <v>1.0648192464</v>
       </c>
       <c r="Q9">
-        <v>3.4000370234</v>
+        <v>3.2448192464</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09955096181752132</v>
+        <v>0.1000138042675304</v>
       </c>
       <c r="T9">
-        <v>1.24136170479264</v>
+        <v>1.252050906871373</v>
       </c>
       <c r="U9">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.215980869135688</v>
+        <v>2.508711084807342</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.096499259926128</v>
+        <v>0.0967641653619612</v>
       </c>
       <c r="C10">
-        <v>144.4156691400152</v>
+        <v>142.0730730691984</v>
       </c>
       <c r="D10">
-        <v>148.0404691400151</v>
+        <v>147.2709730691984</v>
       </c>
       <c r="E10">
-        <v>10.5748</v>
+        <v>12.1479</v>
       </c>
       <c r="F10">
-        <v>12.5848</v>
+        <v>14.1579</v>
       </c>
       <c r="G10">
         <v>8.960000000000001</v>
@@ -2223,45 +2223,45 @@
         <v>2.27</v>
       </c>
       <c r="M10">
-        <v>0.9048471200000001</v>
+        <v>1.07316882</v>
       </c>
       <c r="N10">
-        <v>1.36515288</v>
+        <v>1.19683118</v>
       </c>
       <c r="O10">
-        <v>0.3003336336</v>
+        <v>0.2633028596</v>
       </c>
       <c r="P10">
-        <v>1.0648192464</v>
+        <v>0.9335283204</v>
       </c>
       <c r="Q10">
-        <v>3.2448192464</v>
+        <v>3.1135283204</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1000138042675304</v>
+        <v>0.1004868190790782</v>
       </c>
       <c r="T10">
-        <v>1.252050906871373</v>
+        <v>1.262975036468319</v>
       </c>
       <c r="U10">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.508711084807342</v>
+        <v>2.115231040722931</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2269,81 +2269,81 @@
     </row>
     <row r="11">
       <c r="A11">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="B11">
+        <v>0.09789331079779436</v>
+      </c>
+      <c r="C11">
+        <v>137.307809919552</v>
+      </c>
+      <c r="D11">
+        <v>144.078809919552</v>
+      </c>
+      <c r="E11">
+        <v>13.721</v>
+      </c>
+      <c r="F11">
+        <v>15.731</v>
+      </c>
+      <c r="G11">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="H11">
+        <v>155.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4.45</v>
+      </c>
+      <c r="K11">
+        <v>2.18</v>
+      </c>
+      <c r="L11">
+        <v>2.27</v>
+      </c>
+      <c r="M11">
+        <v>1.41579</v>
+      </c>
+      <c r="N11">
+        <v>0.8542100000000001</v>
+      </c>
+      <c r="O11">
+        <v>0.1879262</v>
+      </c>
+      <c r="P11">
+        <v>0.6662838000000001</v>
+      </c>
+      <c r="Q11">
+        <v>2.8462838</v>
+      </c>
+      <c r="R11">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S11">
+        <v>0.1009703453308826</v>
+      </c>
+      <c r="T11">
+        <v>1.274141924500753</v>
+      </c>
+      <c r="U11">
         <v>0.09</v>
-      </c>
-      <c r="B11">
-        <v>0.0967641653619612</v>
-      </c>
-      <c r="C11">
-        <v>142.0730730691984</v>
-      </c>
-      <c r="D11">
-        <v>147.2709730691984</v>
-      </c>
-      <c r="E11">
-        <v>12.1479</v>
-      </c>
-      <c r="F11">
-        <v>14.1579</v>
-      </c>
-      <c r="G11">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="H11">
-        <v>155.3</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>4.45</v>
-      </c>
-      <c r="K11">
-        <v>2.18</v>
-      </c>
-      <c r="L11">
-        <v>2.27</v>
-      </c>
-      <c r="M11">
-        <v>1.07316882</v>
-      </c>
-      <c r="N11">
-        <v>1.19683118</v>
-      </c>
-      <c r="O11">
-        <v>0.2633028596</v>
-      </c>
-      <c r="P11">
-        <v>0.9335283204</v>
-      </c>
-      <c r="Q11">
-        <v>3.1135283204</v>
-      </c>
-      <c r="R11">
-        <v>0.0989010989010989</v>
-      </c>
-      <c r="S11">
-        <v>0.1004868190790782</v>
-      </c>
-      <c r="T11">
-        <v>1.262975036468319</v>
-      </c>
-      <c r="U11">
-        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.115231040722931</v>
+        <v>1.603345128867982</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09789331079779436</v>
+        <v>0.1034077009191806</v>
       </c>
       <c r="C12">
-        <v>137.307809919552</v>
+        <v>121.9430335734313</v>
       </c>
       <c r="D12">
-        <v>144.078809919552</v>
+        <v>130.2871335734312</v>
       </c>
       <c r="E12">
-        <v>13.721</v>
+        <v>15.2941</v>
       </c>
       <c r="F12">
-        <v>15.731</v>
+        <v>17.3041</v>
       </c>
       <c r="G12">
         <v>8.960000000000001</v>
@@ -2387,45 +2387,45 @@
         <v>2.27</v>
       </c>
       <c r="M12">
-        <v>1.41579</v>
+        <v>2.54024188</v>
       </c>
       <c r="N12">
-        <v>0.8542099999999999</v>
+        <v>-0.2702418800000004</v>
       </c>
       <c r="O12">
-        <v>0.1879262</v>
+        <v>-0.05945321360000008</v>
       </c>
       <c r="P12">
-        <v>0.6662838</v>
+        <v>-0.2107886664000003</v>
       </c>
       <c r="Q12">
-        <v>2.8462838</v>
+        <v>1.9692113336</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1009703453308826</v>
+        <v>0.1016116003082463</v>
       </c>
       <c r="T12">
-        <v>1.274141924500753</v>
+        <v>1.288951508273586</v>
       </c>
       <c r="U12">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V12">
-        <v>0.22</v>
+        <v>0.1965954517685536</v>
       </c>
       <c r="W12">
-        <v>0.0702</v>
+        <v>0.1179397876803763</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y12">
-        <v>1.603345128867982</v>
+        <v>0.8936156898570619</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1034077009191806</v>
+        <v>0.1044177009191806</v>
       </c>
       <c r="C13">
-        <v>121.9430335734313</v>
+        <v>118.1250484475101</v>
       </c>
       <c r="D13">
-        <v>130.2871335734312</v>
+        <v>128.0422484475101</v>
       </c>
       <c r="E13">
-        <v>15.2941</v>
+        <v>16.8672</v>
       </c>
       <c r="F13">
-        <v>17.3041</v>
+        <v>18.8772</v>
       </c>
       <c r="G13">
         <v>8.960000000000001</v>
@@ -2469,37 +2469,37 @@
         <v>2.27</v>
       </c>
       <c r="M13">
-        <v>2.54024188</v>
+        <v>2.77117296</v>
       </c>
       <c r="N13">
-        <v>-0.2702418800000004</v>
+        <v>-0.5011729599999999</v>
       </c>
       <c r="O13">
-        <v>-0.05945321360000008</v>
+        <v>-0.1102580512</v>
       </c>
       <c r="P13">
-        <v>-0.2107886664000003</v>
+        <v>-0.3909149087999999</v>
       </c>
       <c r="Q13">
-        <v>1.9692113336</v>
+        <v>1.7890850912</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1016116003082463</v>
+        <v>0.1022458230390218</v>
       </c>
       <c r="T13">
-        <v>1.288951508273586</v>
+        <v>1.303598684503968</v>
       </c>
       <c r="U13">
         <v>0.1468</v>
       </c>
       <c r="V13">
-        <v>0.1965954517685536</v>
+        <v>0.1802124974545075</v>
       </c>
       <c r="W13">
-        <v>0.1179397876803763</v>
+        <v>0.1203448053736783</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.8936156898570619</v>
+        <v>0.8191477157023068</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1044177009191806</v>
+        <v>0.1127429615611958</v>
       </c>
       <c r="C14">
-        <v>118.1250484475101</v>
+        <v>100.6281669676494</v>
       </c>
       <c r="D14">
-        <v>128.0422484475101</v>
+        <v>112.1184669676494</v>
       </c>
       <c r="E14">
-        <v>16.8672</v>
+        <v>18.4403</v>
       </c>
       <c r="F14">
-        <v>18.8772</v>
+        <v>20.4503</v>
       </c>
       <c r="G14">
         <v>8.960000000000001</v>
@@ -2551,45 +2551,45 @@
         <v>2.27</v>
       </c>
       <c r="M14">
-        <v>2.77117296</v>
+        <v>4.10642024</v>
       </c>
       <c r="N14">
-        <v>-0.5011729599999999</v>
+        <v>-1.83642024</v>
       </c>
       <c r="O14">
-        <v>-0.1102580512</v>
+        <v>-0.4040124528</v>
       </c>
       <c r="P14">
-        <v>-0.3909149087999999</v>
+        <v>-1.4324077872</v>
       </c>
       <c r="Q14">
-        <v>1.7890850912</v>
+        <v>0.7475922127999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1022458230390218</v>
+        <v>0.1032340056509821</v>
       </c>
       <c r="T14">
-        <v>1.303598684503968</v>
+        <v>1.326420453833305</v>
       </c>
       <c r="U14">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.1802124974545075</v>
+        <v>0.1216144405132778</v>
       </c>
       <c r="W14">
-        <v>0.1203448053736783</v>
+        <v>0.1763798203449338</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.8191477157023068</v>
+        <v>0.55279291142399</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2597,22 +2597,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1127429615611958</v>
+        <v>0.1142929615611958</v>
       </c>
       <c r="C15">
-        <v>100.6281669676494</v>
+        <v>96.51781905430596</v>
       </c>
       <c r="D15">
-        <v>112.1184669676494</v>
+        <v>109.581219054306</v>
       </c>
       <c r="E15">
-        <v>18.4403</v>
+        <v>20.0134</v>
       </c>
       <c r="F15">
-        <v>20.4503</v>
+        <v>22.0234</v>
       </c>
       <c r="G15">
         <v>8.960000000000001</v>
@@ -2633,37 +2633,37 @@
         <v>2.27</v>
       </c>
       <c r="M15">
-        <v>4.10642024</v>
+        <v>4.422298720000001</v>
       </c>
       <c r="N15">
-        <v>-1.83642024</v>
+        <v>-2.152298720000001</v>
       </c>
       <c r="O15">
-        <v>-0.4040124528</v>
+        <v>-0.4735057184000001</v>
       </c>
       <c r="P15">
-        <v>-1.4324077872</v>
+        <v>-1.6787930016</v>
       </c>
       <c r="Q15">
-        <v>0.7475922127999999</v>
+        <v>0.5012069983999998</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1032340056509821</v>
+        <v>0.1039018429259935</v>
       </c>
       <c r="T15">
-        <v>1.326420453833305</v>
+        <v>1.341843947482529</v>
       </c>
       <c r="U15">
         <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.1216144405132778</v>
+        <v>0.1129276947623294</v>
       </c>
       <c r="W15">
-        <v>0.1763798203449338</v>
+        <v>0.1781241188917243</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.55279291142399</v>
+        <v>0.5133077034651335</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1142929615611958</v>
+        <v>0.1212121027966021</v>
       </c>
       <c r="C16">
-        <v>96.51781905430596</v>
+        <v>84.89052479016068</v>
       </c>
       <c r="D16">
-        <v>109.581219054306</v>
+        <v>99.52702479016068</v>
       </c>
       <c r="E16">
-        <v>20.0134</v>
+        <v>21.5865</v>
       </c>
       <c r="F16">
-        <v>22.0234</v>
+        <v>23.5965</v>
       </c>
       <c r="G16">
         <v>8.960000000000001</v>
@@ -2715,45 +2715,45 @@
         <v>2.27</v>
       </c>
       <c r="M16">
-        <v>4.422298720000001</v>
+        <v>5.564054700000001</v>
       </c>
       <c r="N16">
-        <v>-2.152298720000001</v>
+        <v>-3.294054700000001</v>
       </c>
       <c r="O16">
-        <v>-0.4735057184000001</v>
+        <v>-0.7246920340000002</v>
       </c>
       <c r="P16">
-        <v>-1.6787930016</v>
+        <v>-2.569362666</v>
       </c>
       <c r="Q16">
-        <v>0.5012069983999998</v>
+        <v>-0.3893626660000002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1039018429259935</v>
+        <v>0.1047255601785419</v>
       </c>
       <c r="T16">
-        <v>1.341843947482529</v>
+        <v>1.360867440612978</v>
       </c>
       <c r="U16">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.1129276947623294</v>
+        <v>0.08975468914782594</v>
       </c>
       <c r="W16">
-        <v>0.1781241188917243</v>
+        <v>0.2146358442989427</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.5133077034651335</v>
+        <v>0.4079758597628452</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.121212102796602</v>
+        <v>0.123112102796602</v>
       </c>
       <c r="C17">
-        <v>84.89052479016073</v>
+        <v>80.87147725722653</v>
       </c>
       <c r="D17">
-        <v>99.52702479016072</v>
+        <v>97.08107725722653</v>
       </c>
       <c r="E17">
-        <v>21.5865</v>
+        <v>23.1596</v>
       </c>
       <c r="F17">
-        <v>23.5965</v>
+        <v>25.1696</v>
       </c>
       <c r="G17">
         <v>8.960000000000001</v>
@@ -2797,37 +2797,37 @@
         <v>2.27</v>
       </c>
       <c r="M17">
-        <v>5.5640547</v>
+        <v>5.93499168</v>
       </c>
       <c r="N17">
-        <v>-3.2940547</v>
+        <v>-3.66499168</v>
       </c>
       <c r="O17">
-        <v>-0.7246920339999999</v>
+        <v>-0.8062981696000001</v>
       </c>
       <c r="P17">
-        <v>-2.569362666</v>
+        <v>-2.8586935104</v>
       </c>
       <c r="Q17">
-        <v>-0.3893626659999998</v>
+        <v>-0.6786935104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1047255601785419</v>
+        <v>0.1054270549425722</v>
       </c>
       <c r="T17">
-        <v>1.360867440612977</v>
+        <v>1.377068243477418</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.08975468914782596</v>
+        <v>0.08414502107608683</v>
       </c>
       <c r="W17">
-        <v>0.2146358442989427</v>
+        <v>0.2159586040302587</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.4079758597628452</v>
+        <v>0.3824773685276674</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2843,22 +2843,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.123112102796602</v>
+        <v>0.125012102796602</v>
       </c>
       <c r="C18">
-        <v>80.87147725722653</v>
+        <v>76.96976786198844</v>
       </c>
       <c r="D18">
-        <v>97.08107725722653</v>
+        <v>94.75246786198845</v>
       </c>
       <c r="E18">
-        <v>23.1596</v>
+        <v>24.7327</v>
       </c>
       <c r="F18">
-        <v>25.1696</v>
+        <v>26.7427</v>
       </c>
       <c r="G18">
         <v>8.960000000000001</v>
@@ -2879,37 +2879,37 @@
         <v>2.27</v>
       </c>
       <c r="M18">
-        <v>5.93499168</v>
+        <v>6.305928660000001</v>
       </c>
       <c r="N18">
-        <v>-3.66499168</v>
+        <v>-4.035928660000001</v>
       </c>
       <c r="O18">
-        <v>-0.8062981696000001</v>
+        <v>-0.8879043052000003</v>
       </c>
       <c r="P18">
-        <v>-2.8586935104</v>
+        <v>-3.148024354800001</v>
       </c>
       <c r="Q18">
-        <v>-0.6786935104</v>
+        <v>-0.9680243548000012</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1054270549425722</v>
+        <v>0.1061454531948923</v>
       </c>
       <c r="T18">
-        <v>1.377068243477418</v>
+        <v>1.393659427133772</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.08414502107608683</v>
+        <v>0.07919531395396406</v>
       </c>
       <c r="W18">
-        <v>0.2159586040302587</v>
+        <v>0.2171257449696553</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3824773685276674</v>
+        <v>0.3599786997907457</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2925,22 +2925,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.125012102796602</v>
+        <v>0.126912102796602</v>
       </c>
       <c r="C19">
-        <v>76.96976786198844</v>
+        <v>73.1771508881871</v>
       </c>
       <c r="D19">
-        <v>94.75246786198845</v>
+        <v>92.53295088818709</v>
       </c>
       <c r="E19">
-        <v>24.7327</v>
+        <v>26.3058</v>
       </c>
       <c r="F19">
-        <v>26.7427</v>
+        <v>28.3158</v>
       </c>
       <c r="G19">
         <v>8.960000000000001</v>
@@ -2961,37 +2961,37 @@
         <v>2.27</v>
       </c>
       <c r="M19">
-        <v>6.305928660000001</v>
+        <v>6.676865640000001</v>
       </c>
       <c r="N19">
-        <v>-4.035928660000001</v>
+        <v>-4.406865640000001</v>
       </c>
       <c r="O19">
-        <v>-0.8879043052000003</v>
+        <v>-0.9695104408000003</v>
       </c>
       <c r="P19">
-        <v>-3.148024354800001</v>
+        <v>-3.437355199200001</v>
       </c>
       <c r="Q19">
-        <v>-0.9680243548000012</v>
+        <v>-1.257355199200001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1061454531948923</v>
+        <v>0.1068813733558057</v>
       </c>
       <c r="T19">
-        <v>1.393659427133772</v>
+        <v>1.410655273806135</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.07919531395396406</v>
+        <v>0.07479557428985495</v>
       </c>
       <c r="W19">
-        <v>0.2171257449696553</v>
+        <v>0.2181632035824522</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3599786997907457</v>
+        <v>0.3399798831357043</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3007,22 +3007,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.126912102796602</v>
+        <v>0.128812102796602</v>
       </c>
       <c r="C20">
-        <v>73.1771508881871</v>
+        <v>69.48613553892366</v>
       </c>
       <c r="D20">
-        <v>92.53295088818709</v>
+        <v>90.41503553892366</v>
       </c>
       <c r="E20">
-        <v>26.3058</v>
+        <v>27.8789</v>
       </c>
       <c r="F20">
-        <v>28.3158</v>
+        <v>29.8889</v>
       </c>
       <c r="G20">
         <v>8.960000000000001</v>
@@ -3043,37 +3043,37 @@
         <v>2.27</v>
       </c>
       <c r="M20">
-        <v>6.67686564</v>
+        <v>7.047802620000001</v>
       </c>
       <c r="N20">
-        <v>-4.406865639999999</v>
+        <v>-4.777802620000001</v>
       </c>
       <c r="O20">
-        <v>-0.9695104407999999</v>
+        <v>-1.0511165764</v>
       </c>
       <c r="P20">
-        <v>-3.4373551992</v>
+        <v>-3.726686043600001</v>
       </c>
       <c r="Q20">
-        <v>-1.2573551992</v>
+        <v>-1.546686043600001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1068813733558057</v>
+        <v>0.1076354643848897</v>
       </c>
       <c r="T20">
-        <v>1.410655273806135</v>
+        <v>1.428070771013618</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07479557428985496</v>
+        <v>0.0708589651167047</v>
       </c>
       <c r="W20">
-        <v>0.2181632035824522</v>
+        <v>0.2190914560254811</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3399798831357045</v>
+        <v>0.3220862050759303</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3089,22 +3089,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.128812102796602</v>
+        <v>0.130712102796602</v>
       </c>
       <c r="C21">
-        <v>69.48613553892366</v>
+        <v>65.8899014759803</v>
       </c>
       <c r="D21">
-        <v>90.41503553892366</v>
+        <v>88.3919014759803</v>
       </c>
       <c r="E21">
-        <v>27.8789</v>
+        <v>29.45200000000001</v>
       </c>
       <c r="F21">
-        <v>29.8889</v>
+        <v>31.462</v>
       </c>
       <c r="G21">
         <v>8.960000000000001</v>
@@ -3125,37 +3125,37 @@
         <v>2.27</v>
       </c>
       <c r="M21">
-        <v>7.047802620000001</v>
+        <v>7.418739600000001</v>
       </c>
       <c r="N21">
-        <v>-4.777802620000001</v>
+        <v>-5.148739600000001</v>
       </c>
       <c r="O21">
-        <v>-1.0511165764</v>
+        <v>-1.132722712</v>
       </c>
       <c r="P21">
-        <v>-3.726686043600001</v>
+        <v>-4.016016888000001</v>
       </c>
       <c r="Q21">
-        <v>-1.546686043600001</v>
+        <v>-1.836016888000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1076354643848897</v>
+        <v>0.1084084076897008</v>
       </c>
       <c r="T21">
-        <v>1.428070771013618</v>
+        <v>1.445921655651289</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.0708589651167047</v>
+        <v>0.06731601686086945</v>
       </c>
       <c r="W21">
-        <v>0.2190914560254811</v>
+        <v>0.219926883224207</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3220862050759303</v>
+        <v>0.305981894822134</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3171,22 +3171,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.130712102796602</v>
+        <v>0.132612102796602</v>
       </c>
       <c r="C22">
-        <v>65.8899014759803</v>
+        <v>62.38222545035574</v>
       </c>
       <c r="D22">
-        <v>88.3919014759803</v>
+        <v>86.45732545035574</v>
       </c>
       <c r="E22">
-        <v>29.45200000000001</v>
+        <v>31.02510000000001</v>
       </c>
       <c r="F22">
-        <v>31.462</v>
+        <v>33.03510000000001</v>
       </c>
       <c r="G22">
         <v>8.960000000000001</v>
@@ -3207,37 +3207,37 @@
         <v>2.27</v>
       </c>
       <c r="M22">
-        <v>7.418739600000001</v>
+        <v>7.789676580000002</v>
       </c>
       <c r="N22">
-        <v>-5.148739600000001</v>
+        <v>-5.519676580000002</v>
       </c>
       <c r="O22">
-        <v>-1.132722712</v>
+        <v>-1.2143288476</v>
       </c>
       <c r="P22">
-        <v>-4.016016888000001</v>
+        <v>-4.305347732400001</v>
       </c>
       <c r="Q22">
-        <v>-1.836016888000001</v>
+        <v>-2.125347732400001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1084084076897008</v>
+        <v>0.1092009191794438</v>
       </c>
       <c r="T22">
-        <v>1.445921655651289</v>
+        <v>1.464224461419026</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.06731601686086945</v>
+        <v>0.0641104922484471</v>
       </c>
       <c r="W22">
-        <v>0.219926883224207</v>
+        <v>0.2206827459278162</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.305981894822134</v>
+        <v>0.2914113284020322</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3253,22 +3253,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.132612102796602</v>
+        <v>0.1345121027966021</v>
       </c>
       <c r="C23">
-        <v>62.38222545035575</v>
+        <v>58.95741736118652</v>
       </c>
       <c r="D23">
-        <v>86.45732545035574</v>
+        <v>84.60561736118652</v>
       </c>
       <c r="E23">
-        <v>31.0251</v>
+        <v>32.59820000000001</v>
       </c>
       <c r="F23">
-        <v>33.0351</v>
+        <v>34.6082</v>
       </c>
       <c r="G23">
         <v>8.960000000000001</v>
@@ -3289,37 +3289,37 @@
         <v>2.27</v>
       </c>
       <c r="M23">
-        <v>7.78967658</v>
+        <v>8.160613560000002</v>
       </c>
       <c r="N23">
-        <v>-5.51967658</v>
+        <v>-5.890613560000002</v>
       </c>
       <c r="O23">
-        <v>-1.2143288476</v>
+        <v>-1.2959349832</v>
       </c>
       <c r="P23">
-        <v>-4.3053477324</v>
+        <v>-4.594678576800002</v>
       </c>
       <c r="Q23">
-        <v>-2.1253477324</v>
+        <v>-2.414678576800001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1092009191794438</v>
+        <v>0.1100137514766162</v>
       </c>
       <c r="T23">
-        <v>1.464224461419026</v>
+        <v>1.482996569898758</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06411049224844712</v>
+        <v>0.06119637896442678</v>
       </c>
       <c r="W23">
-        <v>0.2206827459278162</v>
+        <v>0.2213698938401882</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2914113284020322</v>
+        <v>0.2781653589292126</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3335,22 +3335,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1345121027966021</v>
+        <v>0.136412102796602</v>
       </c>
       <c r="C24">
-        <v>58.95741736118652</v>
+        <v>55.61026435915993</v>
       </c>
       <c r="D24">
-        <v>84.60561736118652</v>
+        <v>82.83156435915994</v>
       </c>
       <c r="E24">
-        <v>32.59820000000001</v>
+        <v>34.1713</v>
       </c>
       <c r="F24">
-        <v>34.6082</v>
+        <v>36.1813</v>
       </c>
       <c r="G24">
         <v>8.960000000000001</v>
@@ -3371,37 +3371,37 @@
         <v>2.27</v>
       </c>
       <c r="M24">
-        <v>8.160613560000002</v>
+        <v>8.53155054</v>
       </c>
       <c r="N24">
-        <v>-5.890613560000002</v>
+        <v>-6.26155054</v>
       </c>
       <c r="O24">
-        <v>-1.2959349832</v>
+        <v>-1.3775411188</v>
       </c>
       <c r="P24">
-        <v>-4.594678576800002</v>
+        <v>-4.8840094212</v>
       </c>
       <c r="Q24">
-        <v>-2.414678576800001</v>
+        <v>-2.7040094212</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1100137514766162</v>
+        <v>0.1108476963009878</v>
       </c>
       <c r="T24">
-        <v>1.482996569898758</v>
+        <v>1.502256265611728</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06119637896442678</v>
+        <v>0.05853566683553867</v>
       </c>
       <c r="W24">
-        <v>0.2213698938401882</v>
+        <v>0.22199728976018</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2781653589292126</v>
+        <v>0.2660712128888121</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3417,22 +3417,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.136412102796602</v>
+        <v>0.138312102796602</v>
       </c>
       <c r="C25">
-        <v>55.61026435915993</v>
+        <v>52.33598183790195</v>
       </c>
       <c r="D25">
-        <v>82.83156435915994</v>
+        <v>81.13038183790195</v>
       </c>
       <c r="E25">
-        <v>34.1713</v>
+        <v>35.74440000000001</v>
       </c>
       <c r="F25">
-        <v>36.1813</v>
+        <v>37.7544</v>
       </c>
       <c r="G25">
         <v>8.960000000000001</v>
@@ -3453,37 +3453,37 @@
         <v>2.27</v>
       </c>
       <c r="M25">
-        <v>8.53155054</v>
+        <v>8.902487520000001</v>
       </c>
       <c r="N25">
-        <v>-6.26155054</v>
+        <v>-6.632487520000002</v>
       </c>
       <c r="O25">
-        <v>-1.3775411188</v>
+        <v>-1.4591472544</v>
       </c>
       <c r="P25">
-        <v>-4.8840094212</v>
+        <v>-5.173340265600001</v>
       </c>
       <c r="Q25">
-        <v>-2.7040094212</v>
+        <v>-2.993340265600001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1108476963009878</v>
+        <v>0.1117035870417903</v>
       </c>
       <c r="T25">
-        <v>1.502256265611728</v>
+        <v>1.522022795422409</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05853566683553867</v>
+        <v>0.05609668071739121</v>
       </c>
       <c r="W25">
-        <v>0.22199728976018</v>
+        <v>0.2225724026868391</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2660712128888121</v>
+        <v>0.2549849123517782</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3499,22 +3499,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.138312102796602</v>
+        <v>0.140212102796602</v>
       </c>
       <c r="C26">
-        <v>52.33598183790196</v>
+        <v>49.13017034301974</v>
       </c>
       <c r="D26">
-        <v>81.13038183790195</v>
+        <v>79.49767034301973</v>
       </c>
       <c r="E26">
-        <v>35.7444</v>
+        <v>37.3175</v>
       </c>
       <c r="F26">
-        <v>37.7544</v>
+        <v>39.3275</v>
       </c>
       <c r="G26">
         <v>8.960000000000001</v>
@@ -3535,37 +3535,37 @@
         <v>2.27</v>
       </c>
       <c r="M26">
-        <v>8.902487519999999</v>
+        <v>9.273424500000001</v>
       </c>
       <c r="N26">
-        <v>-6.63248752</v>
+        <v>-7.003424500000001</v>
       </c>
       <c r="O26">
-        <v>-1.4591472544</v>
+        <v>-1.54075339</v>
       </c>
       <c r="P26">
-        <v>-5.1733402656</v>
+        <v>-5.46267111</v>
       </c>
       <c r="Q26">
-        <v>-2.9933402656</v>
+        <v>-3.28267111</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1117035870417903</v>
+        <v>0.1125823015356808</v>
       </c>
       <c r="T26">
-        <v>1.522022795422409</v>
+        <v>1.542316432694708</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05609668071739122</v>
+        <v>0.05385281348869557</v>
       </c>
       <c r="W26">
-        <v>0.2225724026868391</v>
+        <v>0.2231015065793656</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2549849123517782</v>
+        <v>0.2447855158577071</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3581,22 +3581,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.140212102796602</v>
+        <v>0.142112102796602</v>
       </c>
       <c r="C27">
-        <v>49.13017034301974</v>
+        <v>45.98877758161336</v>
       </c>
       <c r="D27">
-        <v>79.49767034301973</v>
+        <v>77.92937758161335</v>
       </c>
       <c r="E27">
-        <v>37.3175</v>
+        <v>38.89060000000001</v>
       </c>
       <c r="F27">
-        <v>39.3275</v>
+        <v>40.9006</v>
       </c>
       <c r="G27">
         <v>8.960000000000001</v>
@@ -3617,37 +3617,37 @@
         <v>2.27</v>
       </c>
       <c r="M27">
-        <v>9.273424500000001</v>
+        <v>9.644361480000001</v>
       </c>
       <c r="N27">
-        <v>-7.003424500000001</v>
+        <v>-7.374361480000001</v>
       </c>
       <c r="O27">
-        <v>-1.54075339</v>
+        <v>-1.6223595256</v>
       </c>
       <c r="P27">
-        <v>-5.46267111</v>
+        <v>-5.752001954400001</v>
       </c>
       <c r="Q27">
-        <v>-3.28267111</v>
+        <v>-3.572001954400001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1125823015356808</v>
+        <v>0.1134847650699468</v>
       </c>
       <c r="T27">
-        <v>1.542316432694708</v>
+        <v>1.563158546650042</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05385281348869557</v>
+        <v>0.05178155143143805</v>
       </c>
       <c r="W27">
-        <v>0.2231015065793656</v>
+        <v>0.2235899101724669</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2447855158577071</v>
+        <v>0.2353706883247183</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.142112102796602</v>
+        <v>0.144012102796602</v>
       </c>
       <c r="C28">
-        <v>45.98877758161336</v>
+        <v>42.90806484154493</v>
       </c>
       <c r="D28">
-        <v>77.92937758161335</v>
+        <v>76.42176484154494</v>
       </c>
       <c r="E28">
-        <v>38.89060000000001</v>
+        <v>40.4637</v>
       </c>
       <c r="F28">
-        <v>40.9006</v>
+        <v>42.4737</v>
       </c>
       <c r="G28">
         <v>8.960000000000001</v>
@@ -3699,37 +3699,37 @@
         <v>2.27</v>
       </c>
       <c r="M28">
-        <v>9.644361480000001</v>
+        <v>10.01529846</v>
       </c>
       <c r="N28">
-        <v>-7.374361480000001</v>
+        <v>-7.745298460000001</v>
       </c>
       <c r="O28">
-        <v>-1.6223595256</v>
+        <v>-1.7039656612</v>
       </c>
       <c r="P28">
-        <v>-5.752001954400001</v>
+        <v>-6.041332798800001</v>
       </c>
       <c r="Q28">
-        <v>-3.572001954400001</v>
+        <v>-3.861332798800001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1134847650699468</v>
+        <v>0.1144119536325488</v>
       </c>
       <c r="T28">
-        <v>1.563158546650042</v>
+        <v>1.58457167742607</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05178155143143805</v>
+        <v>0.04986371619323664</v>
       </c>
       <c r="W28">
-        <v>0.2235899101724669</v>
+        <v>0.2240421357216348</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2353706883247183</v>
+        <v>0.2266532554238029</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.144012102796602</v>
+        <v>0.1459121027966021</v>
       </c>
       <c r="C29">
-        <v>42.90806484154493</v>
+        <v>39.88457723462447</v>
       </c>
       <c r="D29">
-        <v>76.42176484154494</v>
+        <v>74.97137723462448</v>
       </c>
       <c r="E29">
-        <v>40.4637</v>
+        <v>42.03680000000001</v>
       </c>
       <c r="F29">
-        <v>42.4737</v>
+        <v>44.0468</v>
       </c>
       <c r="G29">
         <v>8.960000000000001</v>
@@ -3781,37 +3781,37 @@
         <v>2.27</v>
       </c>
       <c r="M29">
-        <v>10.01529846</v>
+        <v>10.38623544</v>
       </c>
       <c r="N29">
-        <v>-7.745298460000001</v>
+        <v>-8.116235440000002</v>
       </c>
       <c r="O29">
-        <v>-1.7039656612</v>
+        <v>-1.7855717968</v>
       </c>
       <c r="P29">
-        <v>-6.041332798800001</v>
+        <v>-6.330663643200002</v>
       </c>
       <c r="Q29">
-        <v>-3.861332798800001</v>
+        <v>-4.150663643200001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1144119536325488</v>
+        <v>0.1153648974330009</v>
       </c>
       <c r="T29">
-        <v>1.58457167742607</v>
+        <v>1.606579617390321</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04986371619323664</v>
+        <v>0.04808286918633533</v>
       </c>
       <c r="W29">
-        <v>0.2240421357216348</v>
+        <v>0.2244620594458621</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2266532554238029</v>
+        <v>0.2185584963015241</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3827,22 +3827,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1459121027966021</v>
+        <v>0.147812102796602</v>
       </c>
       <c r="C30">
-        <v>39.88457723462447</v>
+        <v>36.91511726516281</v>
       </c>
       <c r="D30">
-        <v>74.97137723462448</v>
+        <v>73.57501726516281</v>
       </c>
       <c r="E30">
-        <v>42.03680000000001</v>
+        <v>43.60990000000001</v>
       </c>
       <c r="F30">
-        <v>44.0468</v>
+        <v>45.61990000000001</v>
       </c>
       <c r="G30">
         <v>8.960000000000001</v>
@@ -3863,37 +3863,37 @@
         <v>2.27</v>
       </c>
       <c r="M30">
-        <v>10.38623544</v>
+        <v>10.75717242</v>
       </c>
       <c r="N30">
-        <v>-8.116235440000002</v>
+        <v>-8.487172420000002</v>
       </c>
       <c r="O30">
-        <v>-1.7855717968</v>
+        <v>-1.8671779324</v>
       </c>
       <c r="P30">
-        <v>-6.330663643200002</v>
+        <v>-6.619994487600001</v>
       </c>
       <c r="Q30">
-        <v>-4.150663643200001</v>
+        <v>-4.439994487600002</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1153648974330009</v>
+        <v>0.1163446847207896</v>
       </c>
       <c r="T30">
-        <v>1.606579617390321</v>
+        <v>1.629207499325396</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04808286918633533</v>
+        <v>0.04642483921439273</v>
       </c>
       <c r="W30">
-        <v>0.2244620594458621</v>
+        <v>0.2248530229132462</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2185584963015241</v>
+        <v>0.2110219964290578</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3909,22 +3909,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.147812102796602</v>
+        <v>0.149712102796602</v>
       </c>
       <c r="C31">
-        <v>36.91511726516283</v>
+        <v>33.99672129826821</v>
       </c>
       <c r="D31">
-        <v>73.57501726516283</v>
+        <v>72.2297212982682</v>
       </c>
       <c r="E31">
-        <v>43.6099</v>
+        <v>45.183</v>
       </c>
       <c r="F31">
-        <v>45.61989999999999</v>
+        <v>47.193</v>
       </c>
       <c r="G31">
         <v>8.960000000000001</v>
@@ -3945,37 +3945,37 @@
         <v>2.27</v>
       </c>
       <c r="M31">
-        <v>10.75717242</v>
+        <v>11.1281094</v>
       </c>
       <c r="N31">
-        <v>-8.48717242</v>
+        <v>-8.8581094</v>
       </c>
       <c r="O31">
-        <v>-1.8671779324</v>
+        <v>-1.948784068</v>
       </c>
       <c r="P31">
-        <v>-6.619994487600001</v>
+        <v>-6.909325332</v>
       </c>
       <c r="Q31">
-        <v>-4.4399944876</v>
+        <v>-4.729325332</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1163446847207896</v>
+        <v>0.1173524659310866</v>
       </c>
       <c r="T31">
-        <v>1.629207499325396</v>
+        <v>1.652481892172901</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04642483921439274</v>
+        <v>0.04487734457391298</v>
       </c>
       <c r="W31">
-        <v>0.2248530229132462</v>
+        <v>0.2252179221494713</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2110219964290578</v>
+        <v>0.2039879298814226</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3991,22 +3991,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.149712102796602</v>
+        <v>0.151612102796602</v>
       </c>
       <c r="C32">
-        <v>33.99672129826821</v>
+        <v>31.12663856340549</v>
       </c>
       <c r="D32">
-        <v>72.2297212982682</v>
+        <v>70.93273856340549</v>
       </c>
       <c r="E32">
-        <v>45.183</v>
+        <v>46.7561</v>
       </c>
       <c r="F32">
-        <v>47.193</v>
+        <v>48.7661</v>
       </c>
       <c r="G32">
         <v>8.960000000000001</v>
@@ -4027,37 +4027,37 @@
         <v>2.27</v>
       </c>
       <c r="M32">
-        <v>11.1281094</v>
+        <v>11.49904638</v>
       </c>
       <c r="N32">
-        <v>-8.8581094</v>
+        <v>-9.229046380000002</v>
       </c>
       <c r="O32">
-        <v>-1.948784068</v>
+        <v>-2.030390203600001</v>
       </c>
       <c r="P32">
-        <v>-6.909325332</v>
+        <v>-7.198656176400001</v>
       </c>
       <c r="Q32">
-        <v>-4.729325332</v>
+        <v>-5.0186561764</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1173524659310866</v>
+        <v>0.1183894581909574</v>
       </c>
       <c r="T32">
-        <v>1.652481892172901</v>
+        <v>1.676430905102943</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.04487734457391298</v>
+        <v>0.04342968829733513</v>
       </c>
       <c r="W32">
-        <v>0.2252179221494713</v>
+        <v>0.2255592794994884</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2039879298814226</v>
+        <v>0.197407674078796</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4073,22 +4073,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.151612102796602</v>
+        <v>0.153512102796602</v>
       </c>
       <c r="C33">
-        <v>31.12663856340549</v>
+        <v>28.30231238016992</v>
       </c>
       <c r="D33">
-        <v>70.93273856340549</v>
+        <v>69.68151238016992</v>
       </c>
       <c r="E33">
-        <v>46.7561</v>
+        <v>48.32920000000001</v>
       </c>
       <c r="F33">
-        <v>48.7661</v>
+        <v>50.33920000000001</v>
       </c>
       <c r="G33">
         <v>8.960000000000001</v>
@@ -4109,37 +4109,37 @@
         <v>2.27</v>
       </c>
       <c r="M33">
-        <v>11.49904638</v>
+        <v>11.86998336</v>
       </c>
       <c r="N33">
-        <v>-9.229046380000002</v>
+        <v>-9.599983360000001</v>
       </c>
       <c r="O33">
-        <v>-2.030390203600001</v>
+        <v>-2.111996339200001</v>
       </c>
       <c r="P33">
-        <v>-7.198656176400001</v>
+        <v>-7.4879870208</v>
       </c>
       <c r="Q33">
-        <v>-5.0186561764</v>
+        <v>-5.307987020800001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1183894581909574</v>
+        <v>0.1194569502231774</v>
       </c>
       <c r="T33">
-        <v>1.676430905102943</v>
+        <v>1.701084300766222</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.04342968829733513</v>
+        <v>0.04207251053804342</v>
       </c>
       <c r="W33">
-        <v>0.2255592794994884</v>
+        <v>0.2258793020151294</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.197407674078796</v>
+        <v>0.1912386842638336</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4155,22 +4155,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.153512102796602</v>
+        <v>0.155412102796602</v>
       </c>
       <c r="C34">
-        <v>28.30231238016992</v>
+        <v>25.52136333663869</v>
       </c>
       <c r="D34">
-        <v>69.68151238016992</v>
+        <v>68.47366333663868</v>
       </c>
       <c r="E34">
-        <v>48.32920000000001</v>
+        <v>49.9023</v>
       </c>
       <c r="F34">
-        <v>50.33920000000001</v>
+        <v>51.9123</v>
       </c>
       <c r="G34">
         <v>8.960000000000001</v>
@@ -4191,37 +4191,37 @@
         <v>2.27</v>
       </c>
       <c r="M34">
-        <v>11.86998336</v>
+        <v>12.24092034</v>
       </c>
       <c r="N34">
-        <v>-9.599983360000001</v>
+        <v>-9.970920340000001</v>
       </c>
       <c r="O34">
-        <v>-2.111996339200001</v>
+        <v>-2.1936024748</v>
       </c>
       <c r="P34">
-        <v>-7.4879870208</v>
+        <v>-7.777317865200001</v>
       </c>
       <c r="Q34">
-        <v>-5.307987020800001</v>
+        <v>-5.597317865200001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1194569502231774</v>
+        <v>0.120556307689195</v>
       </c>
       <c r="T34">
-        <v>1.701084300766222</v>
+        <v>1.726473618688106</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04207251053804342</v>
+        <v>0.04079758597628452</v>
       </c>
       <c r="W34">
-        <v>0.2258793020151294</v>
+        <v>0.2261799292267921</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1912386842638336</v>
+        <v>0.1854435726194751</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4237,22 +4237,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.155412102796602</v>
+        <v>0.157312102796602</v>
       </c>
       <c r="C35">
-        <v>25.52136333663869</v>
+        <v>22.78157418741767</v>
       </c>
       <c r="D35">
-        <v>68.47366333663868</v>
+        <v>67.30697418741768</v>
       </c>
       <c r="E35">
-        <v>49.9023</v>
+        <v>51.47540000000001</v>
       </c>
       <c r="F35">
-        <v>51.9123</v>
+        <v>53.48540000000001</v>
       </c>
       <c r="G35">
         <v>8.960000000000001</v>
@@ -4273,37 +4273,37 @@
         <v>2.27</v>
       </c>
       <c r="M35">
-        <v>12.24092034</v>
+        <v>12.61185732</v>
       </c>
       <c r="N35">
-        <v>-9.970920340000001</v>
+        <v>-10.34185732</v>
       </c>
       <c r="O35">
-        <v>-2.1936024748</v>
+        <v>-2.2752086104</v>
       </c>
       <c r="P35">
-        <v>-7.777317865200001</v>
+        <v>-8.066648709600003</v>
       </c>
       <c r="Q35">
-        <v>-5.597317865200001</v>
+        <v>-5.886648709600003</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.120556307689195</v>
+        <v>0.1216889790178191</v>
       </c>
       <c r="T35">
-        <v>1.726473618688106</v>
+        <v>1.75263230988035</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04079758597628452</v>
+        <v>0.03959765697698203</v>
       </c>
       <c r="W35">
-        <v>0.2261799292267921</v>
+        <v>0.2264628724848277</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1854435726194751</v>
+        <v>0.1799893498953729</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4319,22 +4319,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.157312102796602</v>
+        <v>0.159212102796602</v>
       </c>
       <c r="C36">
-        <v>22.78157418741767</v>
+        <v>20.08087626971178</v>
       </c>
       <c r="D36">
-        <v>67.30697418741768</v>
+        <v>66.1793762697118</v>
       </c>
       <c r="E36">
-        <v>51.47540000000001</v>
+        <v>53.04850000000001</v>
       </c>
       <c r="F36">
-        <v>53.48540000000001</v>
+        <v>55.05850000000001</v>
       </c>
       <c r="G36">
         <v>8.960000000000001</v>
@@ -4355,37 +4355,37 @@
         <v>2.27</v>
       </c>
       <c r="M36">
-        <v>12.61185732</v>
+        <v>12.9827943</v>
       </c>
       <c r="N36">
-        <v>-10.34185732</v>
+        <v>-10.7127943</v>
       </c>
       <c r="O36">
-        <v>-2.2752086104</v>
+        <v>-2.356814746</v>
       </c>
       <c r="P36">
-        <v>-8.066648709600003</v>
+        <v>-8.355979554000001</v>
       </c>
       <c r="Q36">
-        <v>-5.886648709600003</v>
+        <v>-6.175979554000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1216889790178191</v>
+        <v>0.1228565017719394</v>
       </c>
       <c r="T36">
-        <v>1.75263230988035</v>
+        <v>1.779595883878509</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03959765697698203</v>
+        <v>0.03846629534906826</v>
       </c>
       <c r="W36">
-        <v>0.2264628724848277</v>
+        <v>0.2267296475566897</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1799893498953729</v>
+        <v>0.1748467970412193</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4401,22 +4401,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.159212102796602</v>
+        <v>0.161112102796602</v>
       </c>
       <c r="C37">
-        <v>20.08087626971178</v>
+        <v>17.41733726233157</v>
       </c>
       <c r="D37">
-        <v>66.1793762697118</v>
+        <v>65.08893726233157</v>
       </c>
       <c r="E37">
-        <v>53.04850000000001</v>
+        <v>54.62160000000001</v>
       </c>
       <c r="F37">
-        <v>55.05850000000001</v>
+        <v>56.63160000000001</v>
       </c>
       <c r="G37">
         <v>8.960000000000001</v>
@@ -4437,37 +4437,37 @@
         <v>2.27</v>
       </c>
       <c r="M37">
-        <v>12.9827943</v>
+        <v>13.35373128</v>
       </c>
       <c r="N37">
-        <v>-10.7127943</v>
+        <v>-11.08373128</v>
       </c>
       <c r="O37">
-        <v>-2.356814746</v>
+        <v>-2.4384208816</v>
       </c>
       <c r="P37">
-        <v>-8.355979554000001</v>
+        <v>-8.645310398400001</v>
       </c>
       <c r="Q37">
-        <v>-6.175979554000001</v>
+        <v>-6.465310398400002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1228565017719394</v>
+        <v>0.124060509612126</v>
       </c>
       <c r="T37">
-        <v>1.779595883878509</v>
+        <v>1.807402069564111</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03846629534906826</v>
+        <v>0.03739778714492747</v>
       </c>
       <c r="W37">
-        <v>0.2267296475566897</v>
+        <v>0.2269816017912261</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1748467970412193</v>
+        <v>0.1699899415678522</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4483,22 +4483,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.161112102796602</v>
+        <v>0.163012102796602</v>
       </c>
       <c r="C38">
-        <v>17.41733726233158</v>
+        <v>14.78915013525364</v>
       </c>
       <c r="D38">
-        <v>65.08893726233157</v>
+        <v>64.03385013525364</v>
       </c>
       <c r="E38">
-        <v>54.6216</v>
+        <v>56.1947</v>
       </c>
       <c r="F38">
-        <v>56.6316</v>
+        <v>58.2047</v>
       </c>
       <c r="G38">
         <v>8.960000000000001</v>
@@ -4519,37 +4519,37 @@
         <v>2.27</v>
       </c>
       <c r="M38">
-        <v>13.35373128</v>
+        <v>13.72466826</v>
       </c>
       <c r="N38">
-        <v>-11.08373128</v>
+        <v>-11.45466826</v>
       </c>
       <c r="O38">
-        <v>-2.4384208816</v>
+        <v>-2.5200270172</v>
       </c>
       <c r="P38">
-        <v>-8.645310398399999</v>
+        <v>-8.934641242800001</v>
       </c>
       <c r="Q38">
-        <v>-6.4653103984</v>
+        <v>-6.754641242800002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.124060509612126</v>
+        <v>0.1253027399234296</v>
       </c>
       <c r="T38">
-        <v>1.807402069564111</v>
+        <v>1.836090991303224</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03739778714492748</v>
+        <v>0.03638703614101052</v>
       </c>
       <c r="W38">
-        <v>0.2269816017912261</v>
+        <v>0.2272199368779497</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1699899415678522</v>
+        <v>0.1653956188227751</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4565,22 +4565,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.163012102796602</v>
+        <v>0.164912102796602</v>
       </c>
       <c r="C39">
-        <v>14.78915013525364</v>
+        <v>12.19462315679841</v>
       </c>
       <c r="D39">
-        <v>64.03385013525364</v>
+        <v>63.01242315679841</v>
       </c>
       <c r="E39">
-        <v>56.1947</v>
+        <v>57.7678</v>
       </c>
       <c r="F39">
-        <v>58.2047</v>
+        <v>59.7778</v>
       </c>
       <c r="G39">
         <v>8.960000000000001</v>
@@ -4601,37 +4601,37 @@
         <v>2.27</v>
       </c>
       <c r="M39">
-        <v>13.72466826</v>
+        <v>14.09560524</v>
       </c>
       <c r="N39">
-        <v>-11.45466826</v>
+        <v>-11.82560524</v>
       </c>
       <c r="O39">
-        <v>-2.5200270172</v>
+        <v>-2.6016331528</v>
       </c>
       <c r="P39">
-        <v>-8.934641242800001</v>
+        <v>-9.223972087200002</v>
       </c>
       <c r="Q39">
-        <v>-6.754641242800002</v>
+        <v>-7.043972087200002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1253027399234296</v>
+        <v>0.1265850421802591</v>
       </c>
       <c r="T39">
-        <v>1.836090991303224</v>
+        <v>1.865705362130695</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03638703614101052</v>
+        <v>0.03542948255835235</v>
       </c>
       <c r="W39">
-        <v>0.2272199368779497</v>
+        <v>0.2274457280127405</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1653956188227751</v>
+        <v>0.1610431025379652</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4647,22 +4647,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.164912102796602</v>
+        <v>0.166812102796602</v>
       </c>
       <c r="C40">
-        <v>12.19462315679841</v>
+        <v>9.63217084218612</v>
       </c>
       <c r="D40">
-        <v>63.01242315679841</v>
+        <v>62.02307084218613</v>
       </c>
       <c r="E40">
-        <v>57.7678</v>
+        <v>59.3409</v>
       </c>
       <c r="F40">
-        <v>59.7778</v>
+        <v>61.3509</v>
       </c>
       <c r="G40">
         <v>8.960000000000001</v>
@@ -4683,37 +4683,37 @@
         <v>2.27</v>
       </c>
       <c r="M40">
-        <v>14.09560524</v>
+        <v>14.46654222</v>
       </c>
       <c r="N40">
-        <v>-11.82560524</v>
+        <v>-12.19654222</v>
       </c>
       <c r="O40">
-        <v>-2.6016331528</v>
+        <v>-2.6832392884</v>
       </c>
       <c r="P40">
-        <v>-9.223972087200002</v>
+        <v>-9.513302931600002</v>
       </c>
       <c r="Q40">
-        <v>-7.043972087200002</v>
+        <v>-7.333302931600002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1265850421802591</v>
+        <v>0.1279093871340338</v>
       </c>
       <c r="T40">
-        <v>1.865705362130695</v>
+        <v>1.896290695936116</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03542948255835235</v>
+        <v>0.03452103428762537</v>
       </c>
       <c r="W40">
-        <v>0.2274457280127405</v>
+        <v>0.2276599401149779</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1610431025379652</v>
+        <v>0.1569137922164789</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4729,22 +4729,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.166812102796602</v>
+        <v>0.168712102796602</v>
       </c>
       <c r="C41">
-        <v>9.63217084218612</v>
+        <v>7.100305741607173</v>
       </c>
       <c r="D41">
-        <v>62.02307084218613</v>
+        <v>61.06430574160719</v>
       </c>
       <c r="E41">
-        <v>59.3409</v>
+        <v>60.91400000000001</v>
       </c>
       <c r="F41">
-        <v>61.3509</v>
+        <v>62.92400000000001</v>
       </c>
       <c r="G41">
         <v>8.960000000000001</v>
@@ -4765,37 +4765,37 @@
         <v>2.27</v>
       </c>
       <c r="M41">
-        <v>14.46654222</v>
+        <v>14.8374792</v>
       </c>
       <c r="N41">
-        <v>-12.19654222</v>
+        <v>-12.5674792</v>
       </c>
       <c r="O41">
-        <v>-2.6832392884</v>
+        <v>-2.764845424000001</v>
       </c>
       <c r="P41">
-        <v>-9.513302931600002</v>
+        <v>-9.802633776000002</v>
       </c>
       <c r="Q41">
-        <v>-7.333302931600002</v>
+        <v>-7.622633776000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1279093871340338</v>
+        <v>0.1292778769196011</v>
       </c>
       <c r="T41">
-        <v>1.896290695936116</v>
+        <v>1.927895540868385</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03452103428762537</v>
+        <v>0.03365800843043473</v>
       </c>
       <c r="W41">
-        <v>0.2276599401149779</v>
+        <v>0.2278634416121035</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1569137922164789</v>
+        <v>0.1529909474110669</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.168712102796602</v>
+        <v>0.170612102796602</v>
       </c>
       <c r="C42">
-        <v>7.100305741607173</v>
+        <v>4.597630978347823</v>
       </c>
       <c r="D42">
-        <v>61.06430574160719</v>
+        <v>60.13473097834782</v>
       </c>
       <c r="E42">
-        <v>60.91400000000001</v>
+        <v>62.48710000000001</v>
       </c>
       <c r="F42">
-        <v>62.92400000000001</v>
+        <v>64.4971</v>
       </c>
       <c r="G42">
         <v>8.960000000000001</v>
@@ -4847,37 +4847,37 @@
         <v>2.27</v>
       </c>
       <c r="M42">
-        <v>14.8374792</v>
+        <v>15.20841618</v>
       </c>
       <c r="N42">
-        <v>-12.5674792</v>
+        <v>-12.93841618</v>
       </c>
       <c r="O42">
-        <v>-2.764845424000001</v>
+        <v>-2.846451559600001</v>
       </c>
       <c r="P42">
-        <v>-9.802633776000002</v>
+        <v>-10.0919646204</v>
       </c>
       <c r="Q42">
-        <v>-7.622633776000002</v>
+        <v>-7.911964620400003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1292778769196011</v>
+        <v>0.1306927561894248</v>
       </c>
       <c r="T42">
-        <v>1.927895540868385</v>
+        <v>1.960571736476324</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03365800843043473</v>
+        <v>0.03283708139554608</v>
       </c>
       <c r="W42">
-        <v>0.2278634416121035</v>
+        <v>0.2280570162069303</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1529909474110669</v>
+        <v>0.1492594608888458</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4893,22 +4893,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.170612102796602</v>
+        <v>0.1725121027966021</v>
       </c>
       <c r="C43">
-        <v>4.597630978347823</v>
+        <v>2.12283345824379</v>
       </c>
       <c r="D43">
-        <v>60.13473097834782</v>
+        <v>59.2330334582438</v>
       </c>
       <c r="E43">
-        <v>62.48710000000001</v>
+        <v>64.06020000000001</v>
       </c>
       <c r="F43">
-        <v>64.4971</v>
+        <v>66.07020000000001</v>
       </c>
       <c r="G43">
         <v>8.960000000000001</v>
@@ -4929,37 +4929,37 @@
         <v>2.27</v>
       </c>
       <c r="M43">
-        <v>15.20841618</v>
+        <v>15.57935316</v>
       </c>
       <c r="N43">
-        <v>-12.93841618</v>
+        <v>-13.30935316</v>
       </c>
       <c r="O43">
-        <v>-2.846451559600001</v>
+        <v>-2.928057695200001</v>
       </c>
       <c r="P43">
-        <v>-10.0919646204</v>
+        <v>-10.3812954648</v>
       </c>
       <c r="Q43">
-        <v>-7.911964620400003</v>
+        <v>-8.201295464800003</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1306927561894248</v>
+        <v>0.1321564243995873</v>
       </c>
       <c r="T43">
-        <v>1.960571736476324</v>
+        <v>1.994374697450053</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03283708139554608</v>
+        <v>0.03205524612422355</v>
       </c>
       <c r="W43">
-        <v>0.2280570162069303</v>
+        <v>0.2282413729639081</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1492594608888458</v>
+        <v>0.145705664201016</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4975,22 +4975,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.172512102796602</v>
+        <v>0.174412102796602</v>
       </c>
       <c r="C44">
-        <v>2.122833458243832</v>
+        <v>-0.3253223189612839</v>
       </c>
       <c r="D44">
-        <v>59.23303345824382</v>
+        <v>58.35797768103872</v>
       </c>
       <c r="E44">
-        <v>64.06019999999999</v>
+        <v>65.63329999999999</v>
       </c>
       <c r="F44">
-        <v>66.0702</v>
+        <v>67.6433</v>
       </c>
       <c r="G44">
         <v>8.960000000000001</v>
@@ -5011,37 +5011,37 @@
         <v>2.27</v>
       </c>
       <c r="M44">
-        <v>15.57935316</v>
+        <v>15.95029014</v>
       </c>
       <c r="N44">
-        <v>-13.30935316</v>
+        <v>-13.68029014</v>
       </c>
       <c r="O44">
-        <v>-2.9280576952</v>
+        <v>-3.0096638308</v>
       </c>
       <c r="P44">
-        <v>-10.3812954648</v>
+        <v>-10.6706263092</v>
       </c>
       <c r="Q44">
-        <v>-8.201295464800001</v>
+        <v>-8.4906263092</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1321564243995873</v>
+        <v>0.1336714493890537</v>
       </c>
       <c r="T44">
-        <v>1.994374697450053</v>
+        <v>2.029363727229879</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03205524612422356</v>
+        <v>0.03130977528412533</v>
       </c>
       <c r="W44">
-        <v>0.2282413729639081</v>
+        <v>0.2284171549880032</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1457056642010162</v>
+        <v>0.1423171603823878</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5057,22 +5057,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.174412102796602</v>
+        <v>0.176312102796602</v>
       </c>
       <c r="C45">
-        <v>-0.3253223189612839</v>
+        <v>-2.747999907690954</v>
       </c>
       <c r="D45">
-        <v>58.35797768103872</v>
+        <v>57.50840009230906</v>
       </c>
       <c r="E45">
-        <v>65.63329999999999</v>
+        <v>67.2064</v>
       </c>
       <c r="F45">
-        <v>67.6433</v>
+        <v>69.21640000000001</v>
       </c>
       <c r="G45">
         <v>8.960000000000001</v>
@@ -5093,37 +5093,37 @@
         <v>2.27</v>
       </c>
       <c r="M45">
-        <v>15.95029014</v>
+        <v>16.32122712</v>
       </c>
       <c r="N45">
-        <v>-13.68029014</v>
+        <v>-14.05122712</v>
       </c>
       <c r="O45">
-        <v>-3.0096638308</v>
+        <v>-3.091269966400001</v>
       </c>
       <c r="P45">
-        <v>-10.6706263092</v>
+        <v>-10.9599571536</v>
       </c>
       <c r="Q45">
-        <v>-8.4906263092</v>
+        <v>-8.779957153600003</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1336714493890537</v>
+        <v>0.1352405824138583</v>
       </c>
       <c r="T45">
-        <v>2.029363727229879</v>
+        <v>2.065602365216126</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03130977528412533</v>
+        <v>0.03059818948221339</v>
       </c>
       <c r="W45">
-        <v>0.2284171549880032</v>
+        <v>0.2285849469200941</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1423171603823878</v>
+        <v>0.1390826794646063</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5139,22 +5139,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.176312102796602</v>
+        <v>0.178212102796602</v>
       </c>
       <c r="C46">
-        <v>-2.747999907690954</v>
+        <v>-5.146296078340328</v>
       </c>
       <c r="D46">
-        <v>57.50840009230906</v>
+        <v>56.68320392165968</v>
       </c>
       <c r="E46">
-        <v>67.2064</v>
+        <v>68.7795</v>
       </c>
       <c r="F46">
-        <v>69.21640000000001</v>
+        <v>70.7895</v>
       </c>
       <c r="G46">
         <v>8.960000000000001</v>
@@ -5175,37 +5175,37 @@
         <v>2.27</v>
       </c>
       <c r="M46">
-        <v>16.32122712</v>
+        <v>16.6921641</v>
       </c>
       <c r="N46">
-        <v>-14.05122712</v>
+        <v>-14.4221641</v>
       </c>
       <c r="O46">
-        <v>-3.091269966400001</v>
+        <v>-3.172876102000001</v>
       </c>
       <c r="P46">
-        <v>-10.9599571536</v>
+        <v>-11.249287998</v>
       </c>
       <c r="Q46">
-        <v>-8.779957153600003</v>
+        <v>-9.069287998000004</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1352405824138583</v>
+        <v>0.136866774821383</v>
       </c>
       <c r="T46">
-        <v>2.065602365216126</v>
+        <v>2.10315877185642</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03059818948221339</v>
+        <v>0.02991822971594198</v>
       </c>
       <c r="W46">
-        <v>0.2285849469200941</v>
+        <v>0.2287452814329809</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1390826794646063</v>
+        <v>0.1359919532542817</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5221,22 +5221,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.178212102796602</v>
+        <v>0.1801121027966021</v>
       </c>
       <c r="C47">
-        <v>-5.146296078340328</v>
+        <v>-7.521245540962823</v>
       </c>
       <c r="D47">
-        <v>56.68320392165968</v>
+        <v>55.88135445903718</v>
       </c>
       <c r="E47">
-        <v>68.7795</v>
+        <v>70.3526</v>
       </c>
       <c r="F47">
-        <v>70.7895</v>
+        <v>72.3626</v>
       </c>
       <c r="G47">
         <v>8.960000000000001</v>
@@ -5257,37 +5257,37 @@
         <v>2.27</v>
       </c>
       <c r="M47">
-        <v>16.6921641</v>
+        <v>17.06310108</v>
       </c>
       <c r="N47">
-        <v>-14.4221641</v>
+        <v>-14.79310108</v>
       </c>
       <c r="O47">
-        <v>-3.172876102000001</v>
+        <v>-3.2544822376</v>
       </c>
       <c r="P47">
-        <v>-11.249287998</v>
+        <v>-11.5386188424</v>
       </c>
       <c r="Q47">
-        <v>-9.069287998000004</v>
+        <v>-9.3586188424</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.136866774821383</v>
+        <v>0.1385531965773345</v>
       </c>
       <c r="T47">
-        <v>2.10315877185642</v>
+        <v>2.142106156520428</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02991822971594198</v>
+        <v>0.02926783341776934</v>
       </c>
       <c r="W47">
-        <v>0.2287452814329809</v>
+        <v>0.22889864488009</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1359919532542817</v>
+        <v>0.133035606444406</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5303,22 +5303,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1801121027966021</v>
+        <v>0.1820121027966021</v>
       </c>
       <c r="C48">
-        <v>-7.521245540962823</v>
+        <v>-9.873825273617101</v>
       </c>
       <c r="D48">
-        <v>55.88135445903718</v>
+        <v>55.10187472638292</v>
       </c>
       <c r="E48">
-        <v>70.3526</v>
+        <v>71.92570000000001</v>
       </c>
       <c r="F48">
-        <v>72.3626</v>
+        <v>73.93570000000001</v>
       </c>
       <c r="G48">
         <v>8.960000000000001</v>
@@ -5339,37 +5339,37 @@
         <v>2.27</v>
       </c>
       <c r="M48">
-        <v>17.06310108</v>
+        <v>17.43403806</v>
       </c>
       <c r="N48">
-        <v>-14.79310108</v>
+        <v>-15.16403806</v>
       </c>
       <c r="O48">
-        <v>-3.2544822376</v>
+        <v>-3.336088373200001</v>
       </c>
       <c r="P48">
-        <v>-11.5386188424</v>
+        <v>-11.8279496868</v>
       </c>
       <c r="Q48">
-        <v>-9.3586188424</v>
+        <v>-9.647949686800002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1385531965773345</v>
+        <v>0.1403032568901144</v>
       </c>
       <c r="T48">
-        <v>2.142106156520428</v>
+        <v>2.182523253813266</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02926783341776934</v>
+        <v>0.02864511355781679</v>
       </c>
       <c r="W48">
-        <v>0.22889864488009</v>
+        <v>0.2290454822230668</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.133035606444406</v>
+        <v>0.13020506162644</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5385,22 +5385,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1820121027966021</v>
+        <v>0.183912102796602</v>
       </c>
       <c r="C49">
-        <v>-9.873825273617101</v>
+        <v>-12.20495849344511</v>
       </c>
       <c r="D49">
-        <v>55.10187472638292</v>
+        <v>54.3438415065549</v>
       </c>
       <c r="E49">
-        <v>71.92570000000001</v>
+        <v>73.4988</v>
       </c>
       <c r="F49">
-        <v>73.93570000000001</v>
+        <v>75.50880000000001</v>
       </c>
       <c r="G49">
         <v>8.960000000000001</v>
@@ -5421,37 +5421,37 @@
         <v>2.27</v>
       </c>
       <c r="M49">
-        <v>17.43403806</v>
+        <v>17.80497504</v>
       </c>
       <c r="N49">
-        <v>-15.16403806</v>
+        <v>-15.53497504</v>
       </c>
       <c r="O49">
-        <v>-3.336088373200001</v>
+        <v>-3.417694508800001</v>
       </c>
       <c r="P49">
-        <v>-11.8279496868</v>
+        <v>-12.1172805312</v>
       </c>
       <c r="Q49">
-        <v>-9.647949686800002</v>
+        <v>-9.937280531200003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1403032568901144</v>
+        <v>0.1421206272149243</v>
       </c>
       <c r="T49">
-        <v>2.182523253813266</v>
+        <v>2.224494854848136</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02864511355781679</v>
+        <v>0.02804834035869561</v>
       </c>
       <c r="W49">
-        <v>0.2290454822230668</v>
+        <v>0.2291862013434196</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.13020506162644</v>
+        <v>0.1274924561758891</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5467,22 +5467,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.183912102796602</v>
+        <v>0.185812102796602</v>
       </c>
       <c r="C50">
-        <v>-12.2049584934451</v>
+        <v>-14.5155183044191</v>
       </c>
       <c r="D50">
-        <v>54.3438415065549</v>
+        <v>53.6063816955809</v>
       </c>
       <c r="E50">
-        <v>73.49879999999999</v>
+        <v>75.0719</v>
       </c>
       <c r="F50">
-        <v>75.50879999999999</v>
+        <v>77.0819</v>
       </c>
       <c r="G50">
         <v>8.960000000000001</v>
@@ -5503,37 +5503,37 @@
         <v>2.27</v>
       </c>
       <c r="M50">
-        <v>17.80497504</v>
+        <v>18.17591202</v>
       </c>
       <c r="N50">
-        <v>-15.53497504</v>
+        <v>-15.90591202</v>
       </c>
       <c r="O50">
-        <v>-3.4176945088</v>
+        <v>-3.4993006444</v>
       </c>
       <c r="P50">
-        <v>-12.1172805312</v>
+        <v>-12.4066113756</v>
       </c>
       <c r="Q50">
-        <v>-9.937280531199999</v>
+        <v>-10.2266113756</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1421206272149243</v>
+        <v>0.1440092669642365</v>
       </c>
       <c r="T50">
-        <v>2.224494854848136</v>
+        <v>2.268112401021629</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02804834035869561</v>
+        <v>0.02747592524933447</v>
       </c>
       <c r="W50">
-        <v>0.2291862013434196</v>
+        <v>0.2293211768262069</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1274924561758891</v>
+        <v>0.1248905693151566</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5549,22 +5549,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.185812102796602</v>
+        <v>0.1877121027966021</v>
       </c>
       <c r="C51">
-        <v>-14.5155183044191</v>
+        <v>-16.8063310520597</v>
       </c>
       <c r="D51">
-        <v>53.6063816955809</v>
+        <v>52.8886689479403</v>
       </c>
       <c r="E51">
-        <v>75.0719</v>
+        <v>76.645</v>
       </c>
       <c r="F51">
-        <v>77.0819</v>
+        <v>78.655</v>
       </c>
       <c r="G51">
         <v>8.960000000000001</v>
@@ -5585,37 +5585,37 @@
         <v>2.27</v>
       </c>
       <c r="M51">
-        <v>18.17591202</v>
+        <v>18.546849</v>
       </c>
       <c r="N51">
-        <v>-15.90591202</v>
+        <v>-16.276849</v>
       </c>
       <c r="O51">
-        <v>-3.4993006444</v>
+        <v>-3.58090678</v>
       </c>
       <c r="P51">
-        <v>-12.4066113756</v>
+        <v>-12.69594222</v>
       </c>
       <c r="Q51">
-        <v>-10.2266113756</v>
+        <v>-10.51594222</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1440092669642365</v>
+        <v>0.1459734523035213</v>
       </c>
       <c r="T51">
-        <v>2.268112401021629</v>
+        <v>2.313474649042062</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02747592524933447</v>
+        <v>0.02692640674434778</v>
       </c>
       <c r="W51">
-        <v>0.2293211768262069</v>
+        <v>0.2294507532896828</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1248905693151566</v>
+        <v>0.1223927579288535</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1877121027966021</v>
+        <v>0.1896121027966021</v>
       </c>
       <c r="C52">
-        <v>-16.8063310520597</v>
+        <v>-19.07817941222527</v>
       </c>
       <c r="D52">
-        <v>52.8886689479403</v>
+        <v>52.18992058777473</v>
       </c>
       <c r="E52">
-        <v>76.645</v>
+        <v>78.21809999999999</v>
       </c>
       <c r="F52">
-        <v>78.655</v>
+        <v>80.2281</v>
       </c>
       <c r="G52">
         <v>8.960000000000001</v>
@@ -5667,37 +5667,37 @@
         <v>2.27</v>
       </c>
       <c r="M52">
-        <v>18.546849</v>
+        <v>18.91778598</v>
       </c>
       <c r="N52">
-        <v>-16.276849</v>
+        <v>-16.64778598</v>
       </c>
       <c r="O52">
-        <v>-3.58090678</v>
+        <v>-3.6625129156</v>
       </c>
       <c r="P52">
-        <v>-12.69594222</v>
+        <v>-12.9852730644</v>
       </c>
       <c r="Q52">
-        <v>-10.51594222</v>
+        <v>-10.8052730644</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1459734523035213</v>
+        <v>0.1480178084729809</v>
       </c>
       <c r="T52">
-        <v>2.313474649042062</v>
+        <v>2.360688417389859</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02692640674434778</v>
+        <v>0.02639843798465469</v>
       </c>
       <c r="W52">
-        <v>0.2294507532896828</v>
+        <v>0.2295752483232184</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1223927579288535</v>
+        <v>0.1199928999302485</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5713,22 +5713,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1896121027966021</v>
+        <v>0.191512102796602</v>
       </c>
       <c r="C53">
-        <v>-19.07817941222527</v>
+        <v>-21.33180523824528</v>
       </c>
       <c r="D53">
-        <v>52.18992058777473</v>
+        <v>51.50939476175473</v>
       </c>
       <c r="E53">
-        <v>78.21809999999999</v>
+        <v>79.7912</v>
       </c>
       <c r="F53">
-        <v>80.2281</v>
+        <v>81.80120000000001</v>
       </c>
       <c r="G53">
         <v>8.960000000000001</v>
@@ -5749,37 +5749,37 @@
         <v>2.27</v>
       </c>
       <c r="M53">
-        <v>18.91778598</v>
+        <v>19.28872296</v>
       </c>
       <c r="N53">
-        <v>-16.64778598</v>
+        <v>-17.01872296</v>
       </c>
       <c r="O53">
-        <v>-3.6625129156</v>
+        <v>-3.7441190512</v>
       </c>
       <c r="P53">
-        <v>-12.9852730644</v>
+        <v>-13.2746039088</v>
       </c>
       <c r="Q53">
-        <v>-10.8052730644</v>
+        <v>-11.0946039088</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1480178084729809</v>
+        <v>0.1501473461495013</v>
       </c>
       <c r="T53">
-        <v>2.360688417389859</v>
+        <v>2.409869426085481</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02639843798465469</v>
+        <v>0.02589077571571903</v>
       </c>
       <c r="W53">
-        <v>0.2295752483232184</v>
+        <v>0.2296949550862334</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1199928999302485</v>
+        <v>0.1176853441623592</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.191512102796602</v>
+        <v>0.193412102796602</v>
       </c>
       <c r="C54">
-        <v>-21.33180523824528</v>
+        <v>-23.56791218817125</v>
       </c>
       <c r="D54">
-        <v>51.50939476175473</v>
+        <v>50.84638781182876</v>
       </c>
       <c r="E54">
-        <v>79.7912</v>
+        <v>81.3643</v>
       </c>
       <c r="F54">
-        <v>81.80120000000001</v>
+        <v>83.37430000000001</v>
       </c>
       <c r="G54">
         <v>8.960000000000001</v>
@@ -5831,37 +5831,37 @@
         <v>2.27</v>
       </c>
       <c r="M54">
-        <v>19.28872296</v>
+        <v>19.65965994</v>
       </c>
       <c r="N54">
-        <v>-17.01872296</v>
+        <v>-17.38965994</v>
       </c>
       <c r="O54">
-        <v>-3.7441190512</v>
+        <v>-3.8257251868</v>
       </c>
       <c r="P54">
-        <v>-13.2746039088</v>
+        <v>-13.5639347532</v>
       </c>
       <c r="Q54">
-        <v>-11.0946039088</v>
+        <v>-11.3839347532</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1501473461495013</v>
+        <v>0.1523675024505546</v>
       </c>
       <c r="T54">
-        <v>2.409869426085481</v>
+        <v>2.461143243661768</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02589077571571903</v>
+        <v>0.02540227051353565</v>
       </c>
       <c r="W54">
-        <v>0.2296949550862334</v>
+        <v>0.2298101446129083</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1176853441623592</v>
+        <v>0.1154648659706166</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.193412102796602</v>
+        <v>0.195312102796602</v>
       </c>
       <c r="C55">
-        <v>-23.56791218817125</v>
+        <v>-25.78716815170485</v>
       </c>
       <c r="D55">
-        <v>50.84638781182876</v>
+        <v>50.20023184829515</v>
       </c>
       <c r="E55">
-        <v>81.3643</v>
+        <v>82.9374</v>
       </c>
       <c r="F55">
-        <v>83.37430000000001</v>
+        <v>84.9474</v>
       </c>
       <c r="G55">
         <v>8.960000000000001</v>
@@ -5913,37 +5913,37 @@
         <v>2.27</v>
       </c>
       <c r="M55">
-        <v>19.65965994</v>
+        <v>20.03059692</v>
       </c>
       <c r="N55">
-        <v>-17.38965994</v>
+        <v>-17.76059692</v>
       </c>
       <c r="O55">
-        <v>-3.8257251868</v>
+        <v>-3.9073313224</v>
       </c>
       <c r="P55">
-        <v>-13.5639347532</v>
+        <v>-13.8532655976</v>
       </c>
       <c r="Q55">
-        <v>-11.3839347532</v>
+        <v>-11.6732655976</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1523675024505546</v>
+        <v>0.1546841872864362</v>
       </c>
       <c r="T55">
-        <v>2.461143243661768</v>
+        <v>2.514646357654415</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02540227051353565</v>
+        <v>0.02493185809661832</v>
       </c>
       <c r="W55">
-        <v>0.2298101446129083</v>
+        <v>0.2299210678608174</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1154648659706166</v>
+        <v>0.1133266277119014</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5959,22 +5959,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.195312102796602</v>
+        <v>0.1972121027966021</v>
       </c>
       <c r="C56">
-        <v>-25.78716815170485</v>
+        <v>-27.9902074943999</v>
       </c>
       <c r="D56">
-        <v>50.20023184829515</v>
+        <v>49.57029250560011</v>
       </c>
       <c r="E56">
-        <v>82.9374</v>
+        <v>84.51050000000001</v>
       </c>
       <c r="F56">
-        <v>84.9474</v>
+        <v>86.52050000000001</v>
       </c>
       <c r="G56">
         <v>8.960000000000001</v>
@@ -5995,37 +5995,37 @@
         <v>2.27</v>
       </c>
       <c r="M56">
-        <v>20.03059692</v>
+        <v>20.4015339</v>
       </c>
       <c r="N56">
-        <v>-17.76059692</v>
+        <v>-18.1315339</v>
       </c>
       <c r="O56">
-        <v>-3.9073313224</v>
+        <v>-3.988937458000001</v>
       </c>
       <c r="P56">
-        <v>-13.8532655976</v>
+        <v>-14.142596442</v>
       </c>
       <c r="Q56">
-        <v>-11.6732655976</v>
+        <v>-11.962596442</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1546841872864362</v>
+        <v>0.1571038358928014</v>
       </c>
       <c r="T56">
-        <v>2.514646357654415</v>
+        <v>2.570527387824514</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02493185809661832</v>
+        <v>0.02447855158577071</v>
       </c>
       <c r="W56">
-        <v>0.2299210678608174</v>
+        <v>0.2300279575360753</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1133266277119014</v>
+        <v>0.1112661435716851</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6041,22 +6041,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1972121027966021</v>
+        <v>0.199112102796602</v>
       </c>
       <c r="C57">
-        <v>-27.9902074943999</v>
+        <v>-30.17763313498935</v>
       </c>
       <c r="D57">
-        <v>49.57029250560011</v>
+        <v>48.95596686501066</v>
       </c>
       <c r="E57">
-        <v>84.51050000000001</v>
+        <v>86.0836</v>
       </c>
       <c r="F57">
-        <v>86.52050000000001</v>
+        <v>88.09360000000001</v>
       </c>
       <c r="G57">
         <v>8.960000000000001</v>
@@ -6077,37 +6077,37 @@
         <v>2.27</v>
       </c>
       <c r="M57">
-        <v>20.4015339</v>
+        <v>20.77247088</v>
       </c>
       <c r="N57">
-        <v>-18.1315339</v>
+        <v>-18.50247088</v>
       </c>
       <c r="O57">
-        <v>-3.988937458000001</v>
+        <v>-4.070543593600001</v>
       </c>
       <c r="P57">
-        <v>-14.142596442</v>
+        <v>-14.4319272864</v>
       </c>
       <c r="Q57">
-        <v>-11.962596442</v>
+        <v>-12.2519272864</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1571038358928014</v>
+        <v>0.1596334685267287</v>
       </c>
       <c r="T57">
-        <v>2.570527387824514</v>
+        <v>2.628948464820525</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02447855158577071</v>
+        <v>0.02404143459316766</v>
       </c>
       <c r="W57">
-        <v>0.2300279575360753</v>
+        <v>0.2301310297229311</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1112661435716851</v>
+        <v>0.1092792481507621</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6123,22 +6123,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.199112102796602</v>
+        <v>0.201012102796602</v>
       </c>
       <c r="C58">
-        <v>-30.17763313498935</v>
+        <v>-32.35001847013755</v>
       </c>
       <c r="D58">
-        <v>48.95596686501066</v>
+        <v>48.35668152986246</v>
       </c>
       <c r="E58">
-        <v>86.0836</v>
+        <v>87.6567</v>
       </c>
       <c r="F58">
-        <v>88.09360000000001</v>
+        <v>89.66670000000001</v>
       </c>
       <c r="G58">
         <v>8.960000000000001</v>
@@ -6159,37 +6159,37 @@
         <v>2.27</v>
       </c>
       <c r="M58">
-        <v>20.77247088</v>
+        <v>21.14340786</v>
       </c>
       <c r="N58">
-        <v>-18.50247088</v>
+        <v>-18.87340786</v>
       </c>
       <c r="O58">
-        <v>-4.070543593600001</v>
+        <v>-4.1521497292</v>
       </c>
       <c r="P58">
-        <v>-14.4319272864</v>
+        <v>-14.7212581308</v>
       </c>
       <c r="Q58">
-        <v>-12.2519272864</v>
+        <v>-12.5412581308</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1596334685267287</v>
+        <v>0.1622807584924666</v>
       </c>
       <c r="T58">
-        <v>2.628948464820525</v>
+        <v>2.6900868012117</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02404143459316766</v>
+        <v>0.02361965503890156</v>
       </c>
       <c r="W58">
-        <v>0.2301310297229311</v>
+        <v>0.230230485341827</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1092792481507621</v>
+        <v>0.1073620683586435</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6205,22 +6205,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.201012102796602</v>
+        <v>0.202912102796602</v>
       </c>
       <c r="C59">
-        <v>-32.35001847013755</v>
+        <v>-34.50790915953266</v>
       </c>
       <c r="D59">
-        <v>48.35668152986246</v>
+        <v>47.77189084046736</v>
       </c>
       <c r="E59">
-        <v>87.6567</v>
+        <v>89.22980000000001</v>
       </c>
       <c r="F59">
-        <v>89.66670000000001</v>
+        <v>91.23980000000002</v>
       </c>
       <c r="G59">
         <v>8.960000000000001</v>
@@ -6241,37 +6241,37 @@
         <v>2.27</v>
       </c>
       <c r="M59">
-        <v>21.14340786</v>
+        <v>21.51434484</v>
       </c>
       <c r="N59">
-        <v>-18.87340786</v>
+        <v>-19.24434484</v>
       </c>
       <c r="O59">
-        <v>-4.1521497292</v>
+        <v>-4.233755864800001</v>
       </c>
       <c r="P59">
-        <v>-14.7212581308</v>
+        <v>-15.0105889752</v>
       </c>
       <c r="Q59">
-        <v>-12.5412581308</v>
+        <v>-12.8305889752</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1622807584924666</v>
+        <v>0.1650541098851444</v>
       </c>
       <c r="T59">
-        <v>2.6900868012117</v>
+        <v>2.754136486954835</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02361965503890156</v>
+        <v>0.02321241960719636</v>
       </c>
       <c r="W59">
-        <v>0.230230485341827</v>
+        <v>0.2303265114566231</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1073620683586435</v>
+        <v>0.1055109982145289</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6287,22 +6287,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.202912102796602</v>
+        <v>0.204812102796602</v>
       </c>
       <c r="C60">
-        <v>-34.50790915953263</v>
+        <v>-36.65182478300119</v>
       </c>
       <c r="D60">
-        <v>47.77189084046736</v>
+        <v>47.20107521699881</v>
       </c>
       <c r="E60">
-        <v>89.22979999999998</v>
+        <v>90.80289999999999</v>
       </c>
       <c r="F60">
-        <v>91.23979999999999</v>
+        <v>92.8129</v>
       </c>
       <c r="G60">
         <v>8.960000000000001</v>
@@ -6323,37 +6323,37 @@
         <v>2.27</v>
       </c>
       <c r="M60">
-        <v>21.51434484</v>
+        <v>21.88528182</v>
       </c>
       <c r="N60">
-        <v>-19.24434484</v>
+        <v>-19.61528182</v>
       </c>
       <c r="O60">
-        <v>-4.2337558648</v>
+        <v>-4.3153620004</v>
       </c>
       <c r="P60">
-        <v>-15.0105889752</v>
+        <v>-15.2999198196</v>
       </c>
       <c r="Q60">
-        <v>-12.8305889752</v>
+        <v>-13.1199198196</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1650541098851444</v>
+        <v>0.1679627467116113</v>
       </c>
       <c r="T60">
-        <v>2.754136486954835</v>
+        <v>2.82131054761227</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02321241960719637</v>
+        <v>0.02281898876639643</v>
       </c>
       <c r="W60">
-        <v>0.2303265114566231</v>
+        <v>0.2304192824488837</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1055109982145289</v>
+        <v>0.1037226762108928</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6369,22 +6369,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.204812102796602</v>
+        <v>0.206712102796602</v>
       </c>
       <c r="C61">
-        <v>-36.65182478300119</v>
+        <v>-38.78226038022262</v>
       </c>
       <c r="D61">
-        <v>47.20107521699881</v>
+        <v>46.64373961977738</v>
       </c>
       <c r="E61">
-        <v>90.80289999999999</v>
+        <v>92.37599999999999</v>
       </c>
       <c r="F61">
-        <v>92.8129</v>
+        <v>94.386</v>
       </c>
       <c r="G61">
         <v>8.960000000000001</v>
@@ -6405,37 +6405,37 @@
         <v>2.27</v>
       </c>
       <c r="M61">
-        <v>21.88528182</v>
+        <v>22.2562188</v>
       </c>
       <c r="N61">
-        <v>-19.61528182</v>
+        <v>-19.9862188</v>
       </c>
       <c r="O61">
-        <v>-4.3153620004</v>
+        <v>-4.396968136</v>
       </c>
       <c r="P61">
-        <v>-15.2999198196</v>
+        <v>-15.589250664</v>
       </c>
       <c r="Q61">
-        <v>-13.1199198196</v>
+        <v>-13.409250664</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1679627467116113</v>
+        <v>0.1710168153794016</v>
       </c>
       <c r="T61">
-        <v>2.82131054761227</v>
+        <v>2.891843311302577</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02281898876639643</v>
+        <v>0.02243867228695649</v>
       </c>
       <c r="W61">
-        <v>0.2304192824488837</v>
+        <v>0.2305089610747357</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1037226762108928</v>
+        <v>0.1019939649407113</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6451,22 +6451,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.206712102796602</v>
+        <v>0.2086121027966021</v>
       </c>
       <c r="C62">
-        <v>-38.78226038022262</v>
+        <v>-40.89968788263374</v>
       </c>
       <c r="D62">
-        <v>46.64373961977738</v>
+        <v>46.09941211736626</v>
       </c>
       <c r="E62">
-        <v>92.37599999999999</v>
+        <v>93.94909999999999</v>
       </c>
       <c r="F62">
-        <v>94.386</v>
+        <v>95.95909999999999</v>
       </c>
       <c r="G62">
         <v>8.960000000000001</v>
@@ -6487,37 +6487,37 @@
         <v>2.27</v>
       </c>
       <c r="M62">
-        <v>22.2562188</v>
+        <v>22.62715578</v>
       </c>
       <c r="N62">
-        <v>-19.9862188</v>
+        <v>-20.35715578</v>
       </c>
       <c r="O62">
-        <v>-4.396968136</v>
+        <v>-4.4785742716</v>
       </c>
       <c r="P62">
-        <v>-15.589250664</v>
+        <v>-15.8785815084</v>
       </c>
       <c r="Q62">
-        <v>-13.409250664</v>
+        <v>-13.6985815084</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1710168153794016</v>
+        <v>0.1742275029532324</v>
       </c>
       <c r="T62">
-        <v>2.891843311302577</v>
+        <v>2.965993139797515</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02243867228695649</v>
+        <v>0.02207082520028507</v>
       </c>
       <c r="W62">
-        <v>0.2305089610747357</v>
+        <v>0.2305956994177728</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1019939649407113</v>
+        <v>0.1003219327285685</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6533,22 +6533,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2086121027966021</v>
+        <v>0.210512102796602</v>
       </c>
       <c r="C63">
-        <v>-40.89968788263374</v>
+        <v>-43.00455744622892</v>
       </c>
       <c r="D63">
-        <v>46.09941211736626</v>
+        <v>45.56764255377108</v>
       </c>
       <c r="E63">
-        <v>93.94909999999999</v>
+        <v>95.5222</v>
       </c>
       <c r="F63">
-        <v>95.95909999999999</v>
+        <v>97.5322</v>
       </c>
       <c r="G63">
         <v>8.960000000000001</v>
@@ -6569,37 +6569,37 @@
         <v>2.27</v>
       </c>
       <c r="M63">
-        <v>22.62715578</v>
+        <v>22.99809276</v>
       </c>
       <c r="N63">
-        <v>-20.35715578</v>
+        <v>-20.72809276</v>
       </c>
       <c r="O63">
-        <v>-4.4785742716</v>
+        <v>-4.560180407200001</v>
       </c>
       <c r="P63">
-        <v>-15.8785815084</v>
+        <v>-16.1679123528</v>
       </c>
       <c r="Q63">
-        <v>-13.6985815084</v>
+        <v>-13.9879123528</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1742275029532324</v>
+        <v>0.1776071740835806</v>
       </c>
       <c r="T63">
-        <v>2.965993139797515</v>
+        <v>3.044045590844818</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02207082520028507</v>
+        <v>0.02171484414866756</v>
       </c>
       <c r="W63">
-        <v>0.2305956994177728</v>
+        <v>0.2306796397497442</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1003219327285685</v>
+        <v>0.098703837039398</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6615,22 +6615,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.210512102796602</v>
+        <v>0.2124121027966021</v>
       </c>
       <c r="C64">
-        <v>-43.00455744622892</v>
+        <v>-45.09729869316678</v>
       </c>
       <c r="D64">
-        <v>45.56764255377108</v>
+        <v>45.04800130683321</v>
       </c>
       <c r="E64">
-        <v>95.5222</v>
+        <v>97.09529999999999</v>
       </c>
       <c r="F64">
-        <v>97.5322</v>
+        <v>99.1053</v>
       </c>
       <c r="G64">
         <v>8.960000000000001</v>
@@ -6651,37 +6651,37 @@
         <v>2.27</v>
       </c>
       <c r="M64">
-        <v>22.99809276</v>
+        <v>23.36902974</v>
       </c>
       <c r="N64">
-        <v>-20.72809276</v>
+        <v>-21.09902974</v>
       </c>
       <c r="O64">
-        <v>-4.560180407200001</v>
+        <v>-4.6417865428</v>
       </c>
       <c r="P64">
-        <v>-16.1679123528</v>
+        <v>-16.4572431972</v>
       </c>
       <c r="Q64">
-        <v>-13.9879123528</v>
+        <v>-14.2772431972</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1776071740835806</v>
+        <v>0.1811695301398936</v>
       </c>
       <c r="T64">
-        <v>3.044045590844818</v>
+        <v>3.126317093300083</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02171484414866756</v>
+        <v>0.0213701640828157</v>
       </c>
       <c r="W64">
-        <v>0.2306796397497442</v>
+        <v>0.2307609153092721</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.098703837039398</v>
+        <v>0.09713710946734411</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6697,22 +6697,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2124121027966021</v>
+        <v>0.214312102796602</v>
       </c>
       <c r="C65">
-        <v>-45.09729869316678</v>
+        <v>-47.17832186938099</v>
       </c>
       <c r="D65">
-        <v>45.04800130683321</v>
+        <v>44.54007813061902</v>
       </c>
       <c r="E65">
-        <v>97.09529999999999</v>
+        <v>98.66840000000001</v>
       </c>
       <c r="F65">
-        <v>99.1053</v>
+        <v>100.6784</v>
       </c>
       <c r="G65">
         <v>8.960000000000001</v>
@@ -6733,37 +6733,37 @@
         <v>2.27</v>
       </c>
       <c r="M65">
-        <v>23.36902974</v>
+        <v>23.73996672</v>
       </c>
       <c r="N65">
-        <v>-21.09902974</v>
+        <v>-21.46996672</v>
       </c>
       <c r="O65">
-        <v>-4.6417865428</v>
+        <v>-4.723392678400001</v>
       </c>
       <c r="P65">
-        <v>-16.4572431972</v>
+        <v>-16.7465740416</v>
       </c>
       <c r="Q65">
-        <v>-14.2772431972</v>
+        <v>-14.5665740416</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1811695301398936</v>
+        <v>0.1849297948660018</v>
       </c>
       <c r="T65">
-        <v>3.126317093300083</v>
+        <v>3.213159234780641</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0213701640828157</v>
+        <v>0.02103625526902171</v>
       </c>
       <c r="W65">
-        <v>0.2307609153092721</v>
+        <v>0.2308396510075647</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.09713710946734411</v>
+        <v>0.09561934213191681</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.214312102796602</v>
+        <v>0.2162121027966021</v>
       </c>
       <c r="C66">
-        <v>-47.17832186938099</v>
+        <v>-49.24801892475083</v>
       </c>
       <c r="D66">
-        <v>44.54007813061902</v>
+        <v>44.04348107524918</v>
       </c>
       <c r="E66">
-        <v>98.66840000000001</v>
+        <v>100.2415</v>
       </c>
       <c r="F66">
-        <v>100.6784</v>
+        <v>102.2515</v>
       </c>
       <c r="G66">
         <v>8.960000000000001</v>
@@ -6815,37 +6815,37 @@
         <v>2.27</v>
       </c>
       <c r="M66">
-        <v>23.73996672</v>
+        <v>24.1109037</v>
       </c>
       <c r="N66">
-        <v>-21.46996672</v>
+        <v>-21.8409037</v>
       </c>
       <c r="O66">
-        <v>-4.723392678400001</v>
+        <v>-4.804998814</v>
       </c>
       <c r="P66">
-        <v>-16.7465740416</v>
+        <v>-17.035904886</v>
       </c>
       <c r="Q66">
-        <v>-14.5665740416</v>
+        <v>-14.855904886</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1849297948660018</v>
+        <v>0.1889049318621733</v>
       </c>
       <c r="T66">
-        <v>3.213159234780641</v>
+        <v>3.304963784345803</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02103625526902171</v>
+        <v>0.02071262057257522</v>
       </c>
       <c r="W66">
-        <v>0.2308396510075647</v>
+        <v>0.2309159640689868</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.09561934213191681</v>
+        <v>0.09414827532988734</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6861,22 +6861,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2162121027966021</v>
+        <v>0.218112102796602</v>
       </c>
       <c r="C67">
-        <v>-49.24801892475083</v>
+        <v>-51.30676452180883</v>
       </c>
       <c r="D67">
-        <v>44.04348107524918</v>
+        <v>43.55783547819117</v>
       </c>
       <c r="E67">
-        <v>100.2415</v>
+        <v>101.8146</v>
       </c>
       <c r="F67">
-        <v>102.2515</v>
+        <v>103.8246</v>
       </c>
       <c r="G67">
         <v>8.960000000000001</v>
@@ -6897,37 +6897,37 @@
         <v>2.27</v>
       </c>
       <c r="M67">
-        <v>24.1109037</v>
+        <v>24.48184068</v>
       </c>
       <c r="N67">
-        <v>-21.8409037</v>
+        <v>-22.21184068</v>
       </c>
       <c r="O67">
-        <v>-4.804998814</v>
+        <v>-4.886604949600001</v>
       </c>
       <c r="P67">
-        <v>-17.035904886</v>
+        <v>-17.3252357304</v>
       </c>
       <c r="Q67">
-        <v>-14.855904886</v>
+        <v>-15.1452357304</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1889049318621733</v>
+        <v>0.1931139004463548</v>
       </c>
       <c r="T67">
-        <v>3.304963784345803</v>
+        <v>3.402168601532444</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02071262057257522</v>
+        <v>0.02039879298814226</v>
       </c>
       <c r="W67">
-        <v>0.2309159640689868</v>
+        <v>0.230989964613396</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.09414827532988734</v>
+        <v>0.09272178630973749</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.218112102796602</v>
+        <v>0.220012102796602</v>
       </c>
       <c r="C68">
-        <v>-51.30676452180883</v>
+        <v>-53.3549169784409</v>
       </c>
       <c r="D68">
-        <v>43.55783547819117</v>
+        <v>43.08278302155912</v>
       </c>
       <c r="E68">
-        <v>101.8146</v>
+        <v>103.3877</v>
       </c>
       <c r="F68">
-        <v>103.8246</v>
+        <v>105.3977</v>
       </c>
       <c r="G68">
         <v>8.960000000000001</v>
@@ -6979,37 +6979,37 @@
         <v>2.27</v>
       </c>
       <c r="M68">
-        <v>24.48184068</v>
+        <v>24.85277766</v>
       </c>
       <c r="N68">
-        <v>-22.21184068</v>
+        <v>-22.58277766</v>
       </c>
       <c r="O68">
-        <v>-4.886604949600001</v>
+        <v>-4.968211085200001</v>
       </c>
       <c r="P68">
-        <v>-17.3252357304</v>
+        <v>-17.6145665748</v>
       </c>
       <c r="Q68">
-        <v>-15.1452357304</v>
+        <v>-15.43456657480001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1931139004463548</v>
+        <v>0.1975779580356383</v>
       </c>
       <c r="T68">
-        <v>3.402168601532444</v>
+        <v>3.5052646197607</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02039879298814226</v>
+        <v>0.02009433339130432</v>
       </c>
       <c r="W68">
-        <v>0.230989964613396</v>
+        <v>0.2310617561863305</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.09272178630973749</v>
+        <v>0.09133787905138324</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7025,22 +7025,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.220012102796602</v>
+        <v>0.2219121027966021</v>
       </c>
       <c r="C69">
-        <v>-53.3549169784409</v>
+        <v>-55.39281914956427</v>
       </c>
       <c r="D69">
-        <v>43.08278302155912</v>
+        <v>42.61798085043574</v>
       </c>
       <c r="E69">
-        <v>103.3877</v>
+        <v>104.9608</v>
       </c>
       <c r="F69">
-        <v>105.3977</v>
+        <v>106.9708</v>
       </c>
       <c r="G69">
         <v>8.960000000000001</v>
@@ -7061,37 +7061,37 @@
         <v>2.27</v>
       </c>
       <c r="M69">
-        <v>24.85277766</v>
+        <v>25.22371464</v>
       </c>
       <c r="N69">
-        <v>-22.58277766</v>
+        <v>-22.95371464</v>
       </c>
       <c r="O69">
-        <v>-4.968211085200001</v>
+        <v>-5.049817220800001</v>
       </c>
       <c r="P69">
-        <v>-17.6145665748</v>
+        <v>-17.9038974192</v>
       </c>
       <c r="Q69">
-        <v>-15.43456657480001</v>
+        <v>-15.7238974192</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1975779580356383</v>
+        <v>0.202321019224252</v>
       </c>
       <c r="T69">
-        <v>3.5052646197607</v>
+        <v>3.614804139128222</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02009433339130432</v>
+        <v>0.01979882848849102</v>
       </c>
       <c r="W69">
-        <v>0.2310617561863305</v>
+        <v>0.2311314362424138</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.09133787905138324</v>
+        <v>0.08999467494768643</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7107,22 +7107,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2219121027966021</v>
+        <v>0.2238121027966021</v>
       </c>
       <c r="C70">
-        <v>-55.39281914956427</v>
+        <v>-57.42079925234216</v>
       </c>
       <c r="D70">
-        <v>42.61798085043574</v>
+        <v>42.16310074765785</v>
       </c>
       <c r="E70">
-        <v>104.9608</v>
+        <v>106.5339</v>
       </c>
       <c r="F70">
-        <v>106.9708</v>
+        <v>108.5439</v>
       </c>
       <c r="G70">
         <v>8.960000000000001</v>
@@ -7143,37 +7143,37 @@
         <v>2.27</v>
       </c>
       <c r="M70">
-        <v>25.22371464</v>
+        <v>25.59465162</v>
       </c>
       <c r="N70">
-        <v>-22.95371464</v>
+        <v>-23.32465162</v>
       </c>
       <c r="O70">
-        <v>-5.049817220800001</v>
+        <v>-5.131423356400001</v>
       </c>
       <c r="P70">
-        <v>-17.9038974192</v>
+        <v>-18.19322826360001</v>
       </c>
       <c r="Q70">
-        <v>-15.7238974192</v>
+        <v>-16.01322826360001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.202321019224252</v>
+        <v>0.2073700843605182</v>
       </c>
       <c r="T70">
-        <v>3.614804139128222</v>
+        <v>3.731410724261391</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01979882848849102</v>
+        <v>0.01951188894517955</v>
       </c>
       <c r="W70">
-        <v>0.2311314362424138</v>
+        <v>0.2311990965867267</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08999467494768643</v>
+        <v>0.08869040429627073</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7189,22 +7189,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2238121027966021</v>
+        <v>0.2257121027966021</v>
       </c>
       <c r="C71">
-        <v>-57.42079925234216</v>
+        <v>-59.43917163910938</v>
       </c>
       <c r="D71">
-        <v>42.16310074765785</v>
+        <v>41.71782836089064</v>
       </c>
       <c r="E71">
-        <v>106.5339</v>
+        <v>108.107</v>
       </c>
       <c r="F71">
-        <v>108.5439</v>
+        <v>110.117</v>
       </c>
       <c r="G71">
         <v>8.960000000000001</v>
@@ -7225,37 +7225,37 @@
         <v>2.27</v>
       </c>
       <c r="M71">
-        <v>25.59465162</v>
+        <v>25.9655886</v>
       </c>
       <c r="N71">
-        <v>-23.32465162</v>
+        <v>-23.6955886</v>
       </c>
       <c r="O71">
-        <v>-5.131423356400001</v>
+        <v>-5.213029492000001</v>
       </c>
       <c r="P71">
-        <v>-18.19322826360001</v>
+        <v>-18.482559108</v>
       </c>
       <c r="Q71">
-        <v>-16.01322826360001</v>
+        <v>-16.302559108</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2073700843605182</v>
+        <v>0.2127557538392021</v>
       </c>
       <c r="T71">
-        <v>3.731410724261391</v>
+        <v>3.85579108173677</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01951188894517955</v>
+        <v>0.01923314767453413</v>
       </c>
       <c r="W71">
-        <v>0.2311990965867267</v>
+        <v>0.2312648237783449</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08869040429627073</v>
+        <v>0.08742339852060965</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7271,22 +7271,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2257121027966021</v>
+        <v>0.2276121027966021</v>
       </c>
       <c r="C72">
-        <v>-59.43917163910938</v>
+        <v>-61.44823752183373</v>
       </c>
       <c r="D72">
-        <v>41.71782836089064</v>
+        <v>41.28186247816628</v>
       </c>
       <c r="E72">
-        <v>108.107</v>
+        <v>109.6801</v>
       </c>
       <c r="F72">
-        <v>110.117</v>
+        <v>111.6901</v>
       </c>
       <c r="G72">
         <v>8.960000000000001</v>
@@ -7307,37 +7307,37 @@
         <v>2.27</v>
       </c>
       <c r="M72">
-        <v>25.9655886</v>
+        <v>26.33652558</v>
       </c>
       <c r="N72">
-        <v>-23.6955886</v>
+        <v>-24.06652558</v>
       </c>
       <c r="O72">
-        <v>-5.213029492000001</v>
+        <v>-5.294635627600001</v>
       </c>
       <c r="P72">
-        <v>-18.482559108</v>
+        <v>-18.7718899524</v>
       </c>
       <c r="Q72">
-        <v>-16.302559108</v>
+        <v>-16.5918899524</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2127557538392021</v>
+        <v>0.2185128487991747</v>
       </c>
       <c r="T72">
-        <v>3.85579108173677</v>
+        <v>3.988749394900108</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01923314767453413</v>
+        <v>0.01896225827066745</v>
       </c>
       <c r="W72">
-        <v>0.2312648237783449</v>
+        <v>0.2313286994997766</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.08742339852060965</v>
+        <v>0.08619208304848835</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7353,22 +7353,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.227612102796602</v>
+        <v>0.229512102796602</v>
       </c>
       <c r="C73">
-        <v>-61.4482375218337</v>
+        <v>-63.44828565162216</v>
       </c>
       <c r="D73">
-        <v>41.2818624781663</v>
+        <v>40.85491434837784</v>
       </c>
       <c r="E73">
-        <v>109.6801</v>
+        <v>111.2532</v>
       </c>
       <c r="F73">
-        <v>111.6901</v>
+        <v>113.2632</v>
       </c>
       <c r="G73">
         <v>8.960000000000001</v>
@@ -7389,37 +7389,37 @@
         <v>2.27</v>
       </c>
       <c r="M73">
-        <v>26.33652558</v>
+        <v>26.70746256</v>
       </c>
       <c r="N73">
-        <v>-24.06652558</v>
+        <v>-24.43746256</v>
       </c>
       <c r="O73">
-        <v>-5.2946356276</v>
+        <v>-5.3762417632</v>
       </c>
       <c r="P73">
-        <v>-18.7718899524</v>
+        <v>-19.0612207968</v>
       </c>
       <c r="Q73">
-        <v>-16.5918899524</v>
+        <v>-16.8812207968</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2185128487991746</v>
+        <v>0.2246811648277166</v>
       </c>
       <c r="T73">
-        <v>3.988749394900106</v>
+        <v>4.131204730432253</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01896225827066746</v>
+        <v>0.01869889357246374</v>
       </c>
       <c r="W73">
-        <v>0.2313286994997766</v>
+        <v>0.231390800895613</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.08619208304848847</v>
+        <v>0.08499497078392604</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7435,22 +7435,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.229512102796602</v>
+        <v>0.231412102796602</v>
       </c>
       <c r="C74">
-        <v>-63.44828565162216</v>
+        <v>-65.4395929564927</v>
       </c>
       <c r="D74">
-        <v>40.85491434837784</v>
+        <v>40.4367070435073</v>
       </c>
       <c r="E74">
-        <v>111.2532</v>
+        <v>112.8263</v>
       </c>
       <c r="F74">
-        <v>113.2632</v>
+        <v>114.8363</v>
       </c>
       <c r="G74">
         <v>8.960000000000001</v>
@@ -7471,37 +7471,37 @@
         <v>2.27</v>
       </c>
       <c r="M74">
-        <v>26.70746256</v>
+        <v>27.07839954</v>
       </c>
       <c r="N74">
-        <v>-24.43746256</v>
+        <v>-24.80839954</v>
       </c>
       <c r="O74">
-        <v>-5.3762417632</v>
+        <v>-5.4578478988</v>
       </c>
       <c r="P74">
-        <v>-19.0612207968</v>
+        <v>-19.3505516412</v>
       </c>
       <c r="Q74">
-        <v>-16.8812207968</v>
+        <v>-17.1705516412</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2246811648277166</v>
+        <v>0.231306393154669</v>
       </c>
       <c r="T74">
-        <v>4.131204730432253</v>
+        <v>4.284212313040855</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01869889357246374</v>
+        <v>0.01844274434544369</v>
       </c>
       <c r="W74">
-        <v>0.231390800895613</v>
+        <v>0.2314512008833444</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.08499497078392604</v>
+        <v>0.0838306561156531</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7517,22 +7517,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.231412102796602</v>
+        <v>0.233312102796602</v>
       </c>
       <c r="C75">
-        <v>-65.4395929564927</v>
+        <v>-67.42242514037207</v>
       </c>
       <c r="D75">
-        <v>40.4367070435073</v>
+        <v>40.02697485962794</v>
       </c>
       <c r="E75">
-        <v>112.8263</v>
+        <v>114.3994</v>
       </c>
       <c r="F75">
-        <v>114.8363</v>
+        <v>116.4094</v>
       </c>
       <c r="G75">
         <v>8.960000000000001</v>
@@ -7553,37 +7553,37 @@
         <v>2.27</v>
       </c>
       <c r="M75">
-        <v>27.07839954</v>
+        <v>27.44933652</v>
       </c>
       <c r="N75">
-        <v>-24.80839954</v>
+        <v>-25.17933652</v>
       </c>
       <c r="O75">
-        <v>-5.4578478988</v>
+        <v>-5.539454034400001</v>
       </c>
       <c r="P75">
-        <v>-19.3505516412</v>
+        <v>-19.6398824856</v>
       </c>
       <c r="Q75">
-        <v>-17.1705516412</v>
+        <v>-17.4598824856</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.231306393154669</v>
+        <v>0.2384412544298486</v>
       </c>
       <c r="T75">
-        <v>4.284212313040855</v>
+        <v>4.448989709696272</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01844274434544369</v>
+        <v>0.01819351807050526</v>
       </c>
       <c r="W75">
-        <v>0.2314512008833444</v>
+        <v>0.2315099684389749</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0838306561156531</v>
+        <v>0.08269780941138749</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7599,22 +7599,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.233312102796602</v>
+        <v>0.235212102796602</v>
       </c>
       <c r="C76">
-        <v>-67.42242514037207</v>
+        <v>-69.39703724604232</v>
       </c>
       <c r="D76">
-        <v>40.02697485962794</v>
+        <v>39.62546275395768</v>
       </c>
       <c r="E76">
-        <v>114.3994</v>
+        <v>115.9725</v>
       </c>
       <c r="F76">
-        <v>116.4094</v>
+        <v>117.9825</v>
       </c>
       <c r="G76">
         <v>8.960000000000001</v>
@@ -7635,37 +7635,37 @@
         <v>2.27</v>
       </c>
       <c r="M76">
-        <v>27.44933652</v>
+        <v>27.8202735</v>
       </c>
       <c r="N76">
-        <v>-25.17933652</v>
+        <v>-25.5502735</v>
       </c>
       <c r="O76">
-        <v>-5.539454034400001</v>
+        <v>-5.621060170000001</v>
       </c>
       <c r="P76">
-        <v>-19.6398824856</v>
+        <v>-19.92921333</v>
       </c>
       <c r="Q76">
-        <v>-17.4598824856</v>
+        <v>-17.74921333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2384412544298486</v>
+        <v>0.2461469046070425</v>
       </c>
       <c r="T76">
-        <v>4.448989709696272</v>
+        <v>4.626949298084123</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01819351807050526</v>
+        <v>0.01795093782956519</v>
       </c>
       <c r="W76">
-        <v>0.2315099684389749</v>
+        <v>0.2315671688597885</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.08269780941138749</v>
+        <v>0.08159517195256905</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7681,22 +7681,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.235212102796602</v>
+        <v>0.2371121027966021</v>
       </c>
       <c r="C77">
-        <v>-69.39703724604232</v>
+        <v>-71.36367418454205</v>
       </c>
       <c r="D77">
-        <v>39.62546275395768</v>
+        <v>39.23192581545796</v>
       </c>
       <c r="E77">
-        <v>115.9725</v>
+        <v>117.5456</v>
       </c>
       <c r="F77">
-        <v>117.9825</v>
+        <v>119.5556</v>
       </c>
       <c r="G77">
         <v>8.960000000000001</v>
@@ -7717,37 +7717,37 @@
         <v>2.27</v>
       </c>
       <c r="M77">
-        <v>27.8202735</v>
+        <v>28.19121048</v>
       </c>
       <c r="N77">
-        <v>-25.5502735</v>
+        <v>-25.92121048</v>
       </c>
       <c r="O77">
-        <v>-5.621060170000001</v>
+        <v>-5.7026663056</v>
       </c>
       <c r="P77">
-        <v>-19.92921333</v>
+        <v>-20.2185441744</v>
       </c>
       <c r="Q77">
-        <v>-17.74921333</v>
+        <v>-18.0385441744</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2461469046070425</v>
+        <v>0.2544946922990027</v>
       </c>
       <c r="T77">
-        <v>4.626949298084123</v>
+        <v>4.819738852170962</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01795093782956519</v>
+        <v>0.01771474127917617</v>
       </c>
       <c r="W77">
-        <v>0.2315671688597885</v>
+        <v>0.2316228640063703</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.08159517195256905</v>
+        <v>0.08052155126898264</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7763,22 +7763,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2371121027966021</v>
+        <v>0.239012102796602</v>
       </c>
       <c r="C78">
-        <v>-71.36367418454205</v>
+        <v>-73.3225712333317</v>
       </c>
       <c r="D78">
-        <v>39.23192581545796</v>
+        <v>38.84612876666831</v>
       </c>
       <c r="E78">
-        <v>117.5456</v>
+        <v>119.1187</v>
       </c>
       <c r="F78">
-        <v>119.5556</v>
+        <v>121.1287</v>
       </c>
       <c r="G78">
         <v>8.960000000000001</v>
@@ -7799,37 +7799,37 @@
         <v>2.27</v>
       </c>
       <c r="M78">
-        <v>28.19121048</v>
+        <v>28.56214746</v>
       </c>
       <c r="N78">
-        <v>-25.92121048</v>
+        <v>-26.29214746</v>
       </c>
       <c r="O78">
-        <v>-5.7026663056</v>
+        <v>-5.784272441200001</v>
       </c>
       <c r="P78">
-        <v>-20.2185441744</v>
+        <v>-20.5078750188</v>
       </c>
       <c r="Q78">
-        <v>-18.0385441744</v>
+        <v>-18.3278750188</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2544946922990027</v>
+        <v>0.2635683745728723</v>
       </c>
       <c r="T78">
-        <v>4.819738852170962</v>
+        <v>5.02929271530883</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01771474127917617</v>
+        <v>0.01748467970412194</v>
       </c>
       <c r="W78">
-        <v>0.2316228640063703</v>
+        <v>0.2316771125257681</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.08052155126898264</v>
+        <v>0.07947581683691785</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7845,22 +7845,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.239012102796602</v>
+        <v>0.240912102796602</v>
       </c>
       <c r="C79">
-        <v>-73.3225712333317</v>
+        <v>-75.27395450535204</v>
       </c>
       <c r="D79">
-        <v>38.84612876666831</v>
+        <v>38.46784549464797</v>
       </c>
       <c r="E79">
-        <v>119.1187</v>
+        <v>120.6918</v>
       </c>
       <c r="F79">
-        <v>121.1287</v>
+        <v>122.7018</v>
       </c>
       <c r="G79">
         <v>8.960000000000001</v>
@@ -7881,37 +7881,37 @@
         <v>2.27</v>
       </c>
       <c r="M79">
-        <v>28.56214746</v>
+        <v>28.93308444</v>
       </c>
       <c r="N79">
-        <v>-26.29214746</v>
+        <v>-26.66308444</v>
       </c>
       <c r="O79">
-        <v>-5.784272441200001</v>
+        <v>-5.8658785768</v>
       </c>
       <c r="P79">
-        <v>-20.5078750188</v>
+        <v>-20.7972058632</v>
       </c>
       <c r="Q79">
-        <v>-18.3278750188</v>
+        <v>-18.6172058632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2635683745728723</v>
+        <v>0.2734669370534574</v>
       </c>
       <c r="T79">
-        <v>5.02929271530883</v>
+        <v>5.25789692964105</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01748467970412194</v>
+        <v>0.01726051714381268</v>
       </c>
       <c r="W79">
-        <v>0.2316771125257681</v>
+        <v>0.231729970057489</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07947581683691785</v>
+        <v>0.07845689610823947</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7927,22 +7927,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.240912102796602</v>
+        <v>0.242812102796602</v>
       </c>
       <c r="C80">
-        <v>-75.27395450535204</v>
+        <v>-77.21804139094093</v>
       </c>
       <c r="D80">
-        <v>38.46784549464797</v>
+        <v>38.09685860905907</v>
       </c>
       <c r="E80">
-        <v>120.6918</v>
+        <v>122.2649</v>
       </c>
       <c r="F80">
-        <v>122.7018</v>
+        <v>124.2749</v>
       </c>
       <c r="G80">
         <v>8.960000000000001</v>
@@ -7963,37 +7963,37 @@
         <v>2.27</v>
       </c>
       <c r="M80">
-        <v>28.93308444</v>
+        <v>29.30402142</v>
       </c>
       <c r="N80">
-        <v>-26.66308444</v>
+        <v>-27.03402142</v>
       </c>
       <c r="O80">
-        <v>-5.8658785768</v>
+        <v>-5.947484712400001</v>
       </c>
       <c r="P80">
-        <v>-20.7972058632</v>
+        <v>-21.0865367076</v>
       </c>
       <c r="Q80">
-        <v>-18.6172058632</v>
+        <v>-18.9065367076</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2734669370534574</v>
+        <v>0.2843082197702888</v>
       </c>
       <c r="T80">
-        <v>5.25789692964105</v>
+        <v>5.508272973909672</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01726051714381268</v>
+        <v>0.01704202958503024</v>
       </c>
       <c r="W80">
-        <v>0.231729970057489</v>
+        <v>0.2317814894238499</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07845689610823947</v>
+        <v>0.0774637708410465</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8009,22 +8009,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.242812102796602</v>
+        <v>0.244712102796602</v>
       </c>
       <c r="C81">
-        <v>-77.21804139094093</v>
+        <v>-79.15504097442295</v>
       </c>
       <c r="D81">
-        <v>38.09685860905907</v>
+        <v>37.73295902557706</v>
       </c>
       <c r="E81">
-        <v>122.2649</v>
+        <v>123.838</v>
       </c>
       <c r="F81">
-        <v>124.2749</v>
+        <v>125.848</v>
       </c>
       <c r="G81">
         <v>8.960000000000001</v>
@@ -8045,37 +8045,37 @@
         <v>2.27</v>
       </c>
       <c r="M81">
-        <v>29.30402142</v>
+        <v>29.6749584</v>
       </c>
       <c r="N81">
-        <v>-27.03402142</v>
+        <v>-27.40495840000001</v>
       </c>
       <c r="O81">
-        <v>-5.947484712400001</v>
+        <v>-6.029090848000001</v>
       </c>
       <c r="P81">
-        <v>-21.0865367076</v>
+        <v>-21.375867552</v>
       </c>
       <c r="Q81">
-        <v>-18.9065367076</v>
+        <v>-19.195867552</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2843082197702888</v>
+        <v>0.2962336307588033</v>
       </c>
       <c r="T81">
-        <v>5.508272973909672</v>
+        <v>5.783686622605156</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01704202958503024</v>
+        <v>0.01682900421521736</v>
       </c>
       <c r="W81">
-        <v>0.2317814894238499</v>
+        <v>0.2318317208060517</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.0774637708410465</v>
+        <v>0.07649547370553345</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8091,22 +8091,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.244712102796602</v>
+        <v>0.2466121027966021</v>
       </c>
       <c r="C82">
-        <v>-79.15504097442295</v>
+        <v>-81.08515442704942</v>
       </c>
       <c r="D82">
-        <v>37.73295902557706</v>
+        <v>37.37594557295059</v>
       </c>
       <c r="E82">
-        <v>123.838</v>
+        <v>125.4111</v>
       </c>
       <c r="F82">
-        <v>125.848</v>
+        <v>127.4211</v>
       </c>
       <c r="G82">
         <v>8.960000000000001</v>
@@ -8127,37 +8127,37 @@
         <v>2.27</v>
       </c>
       <c r="M82">
-        <v>29.6749584</v>
+        <v>30.04589538</v>
       </c>
       <c r="N82">
-        <v>-27.40495840000001</v>
+        <v>-27.77589538000001</v>
       </c>
       <c r="O82">
-        <v>-6.029090848000001</v>
+        <v>-6.110696983600001</v>
       </c>
       <c r="P82">
-        <v>-21.375867552</v>
+        <v>-21.6651983964</v>
       </c>
       <c r="Q82">
-        <v>-19.195867552</v>
+        <v>-19.4851983964</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2962336307588033</v>
+        <v>0.3094143481671613</v>
       </c>
       <c r="T82">
-        <v>5.783686622605156</v>
+        <v>6.088091181689637</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01682900421521736</v>
+        <v>0.01662123873107888</v>
       </c>
       <c r="W82">
-        <v>0.2318317208060517</v>
+        <v>0.2318807119072116</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.07649547370553345</v>
+        <v>0.07555108514126763</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8173,22 +8173,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2466121027966021</v>
+        <v>0.248512102796602</v>
       </c>
       <c r="C83">
-        <v>-81.08515442704942</v>
+        <v>-83.00857537784069</v>
       </c>
       <c r="D83">
-        <v>37.37594557295059</v>
+        <v>37.02562462215931</v>
       </c>
       <c r="E83">
-        <v>125.4111</v>
+        <v>126.9842</v>
       </c>
       <c r="F83">
-        <v>127.4211</v>
+        <v>128.9942</v>
       </c>
       <c r="G83">
         <v>8.960000000000001</v>
@@ -8209,37 +8209,37 @@
         <v>2.27</v>
       </c>
       <c r="M83">
-        <v>30.04589538</v>
+        <v>30.41683236</v>
       </c>
       <c r="N83">
-        <v>-27.77589538000001</v>
+        <v>-28.14683236</v>
       </c>
       <c r="O83">
-        <v>-6.110696983600001</v>
+        <v>-6.192303119200001</v>
       </c>
       <c r="P83">
-        <v>-21.6651983964</v>
+        <v>-21.9545292408</v>
       </c>
       <c r="Q83">
-        <v>-19.4851983964</v>
+        <v>-19.7745292408</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3094143481671613</v>
+        <v>0.3240595897320037</v>
       </c>
       <c r="T83">
-        <v>6.088091181689637</v>
+        <v>6.426318469561285</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01662123873107888</v>
+        <v>0.01641854069777304</v>
       </c>
       <c r="W83">
-        <v>0.2318807119072116</v>
+        <v>0.2319285081034651</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07555108514126763</v>
+        <v>0.07462973044442289</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8255,22 +8255,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.248512102796602</v>
+        <v>0.250412102796602</v>
       </c>
       <c r="C84">
-        <v>-83.00857537784069</v>
+        <v>-84.92549026376676</v>
       </c>
       <c r="D84">
-        <v>37.02562462215931</v>
+        <v>36.68180973623326</v>
       </c>
       <c r="E84">
-        <v>126.9842</v>
+        <v>128.5573</v>
       </c>
       <c r="F84">
-        <v>128.9942</v>
+        <v>130.5673</v>
       </c>
       <c r="G84">
         <v>8.960000000000001</v>
@@ -8291,37 +8291,37 @@
         <v>2.27</v>
       </c>
       <c r="M84">
-        <v>30.41683236</v>
+        <v>30.78776934</v>
       </c>
       <c r="N84">
-        <v>-28.14683236</v>
+        <v>-28.51776934</v>
       </c>
       <c r="O84">
-        <v>-6.192303119200001</v>
+        <v>-6.273909254800001</v>
       </c>
       <c r="P84">
-        <v>-21.9545292408</v>
+        <v>-22.24386008520001</v>
       </c>
       <c r="Q84">
-        <v>-19.7745292408</v>
+        <v>-20.06386008520001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3240595897320037</v>
+        <v>0.3404278008927097</v>
       </c>
       <c r="T84">
-        <v>6.426318469561285</v>
+        <v>6.804337203064891</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01641854069777304</v>
+        <v>0.01622072695442638</v>
       </c>
       <c r="W84">
-        <v>0.2319285081034651</v>
+        <v>0.2319751525841463</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.07462973044442289</v>
+        <v>0.0737305770655744</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8337,22 +8337,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.250412102796602</v>
+        <v>0.252312102796602</v>
       </c>
       <c r="C85">
-        <v>-84.92549026376676</v>
+        <v>-86.83607866059688</v>
       </c>
       <c r="D85">
-        <v>36.68180973623326</v>
+        <v>36.34432133940314</v>
       </c>
       <c r="E85">
-        <v>128.5573</v>
+        <v>130.1304</v>
       </c>
       <c r="F85">
-        <v>130.5673</v>
+        <v>132.1404</v>
       </c>
       <c r="G85">
         <v>8.960000000000001</v>
@@ -8373,37 +8373,37 @@
         <v>2.27</v>
       </c>
       <c r="M85">
-        <v>30.78776934</v>
+        <v>31.15870632000001</v>
       </c>
       <c r="N85">
-        <v>-28.51776934</v>
+        <v>-28.88870632000001</v>
       </c>
       <c r="O85">
-        <v>-6.273909254800001</v>
+        <v>-6.355515390400002</v>
       </c>
       <c r="P85">
-        <v>-22.24386008520001</v>
+        <v>-22.53319092960001</v>
       </c>
       <c r="Q85">
-        <v>-20.06386008520001</v>
+        <v>-20.35319092960001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3404278008927097</v>
+        <v>0.3588420384485042</v>
       </c>
       <c r="T85">
-        <v>6.804337203064891</v>
+        <v>7.229608278256447</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01622072695442638</v>
+        <v>0.01602762306211178</v>
       </c>
       <c r="W85">
-        <v>0.2319751525841463</v>
+        <v>0.232020686481954</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.0737305770655744</v>
+        <v>0.07285283210050808</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8419,22 +8419,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.252312102796602</v>
+        <v>0.254212102796602</v>
       </c>
       <c r="C86">
-        <v>-86.83607866059685</v>
+        <v>-88.74051359565223</v>
       </c>
       <c r="D86">
-        <v>36.34432133940314</v>
+        <v>36.01298640434777</v>
       </c>
       <c r="E86">
-        <v>130.1304</v>
+        <v>131.7035</v>
       </c>
       <c r="F86">
-        <v>132.1404</v>
+        <v>133.7135</v>
       </c>
       <c r="G86">
         <v>8.960000000000001</v>
@@ -8455,37 +8455,37 @@
         <v>2.27</v>
       </c>
       <c r="M86">
-        <v>31.15870632</v>
+        <v>31.5296433</v>
       </c>
       <c r="N86">
-        <v>-28.88870632</v>
+        <v>-29.2596433</v>
       </c>
       <c r="O86">
-        <v>-6.3555153904</v>
+        <v>-6.437121526000001</v>
       </c>
       <c r="P86">
-        <v>-22.5331909296</v>
+        <v>-22.822521774</v>
       </c>
       <c r="Q86">
-        <v>-20.3531909296</v>
+        <v>-20.642521774</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3588420384485039</v>
+        <v>0.3797115076784042</v>
       </c>
       <c r="T86">
-        <v>7.229608278256442</v>
+        <v>7.711582163473539</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01602762306211178</v>
+        <v>0.01583906279079281</v>
       </c>
       <c r="W86">
-        <v>0.232020686481954</v>
+        <v>0.232065148993931</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.07285283210050808</v>
+        <v>0.07199573995814912</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8501,22 +8501,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.254212102796602</v>
+        <v>0.256112102796602</v>
       </c>
       <c r="C87">
-        <v>-88.74051359565223</v>
+        <v>-90.63896184360557</v>
       </c>
       <c r="D87">
-        <v>36.01298640434777</v>
+        <v>35.68763815639442</v>
       </c>
       <c r="E87">
-        <v>131.7035</v>
+        <v>133.2766</v>
       </c>
       <c r="F87">
-        <v>133.7135</v>
+        <v>135.2866</v>
       </c>
       <c r="G87">
         <v>8.960000000000001</v>
@@ -8537,37 +8537,37 @@
         <v>2.27</v>
       </c>
       <c r="M87">
-        <v>31.5296433</v>
+        <v>31.90058028</v>
       </c>
       <c r="N87">
-        <v>-29.2596433</v>
+        <v>-29.63058028</v>
       </c>
       <c r="O87">
-        <v>-6.437121526000001</v>
+        <v>-6.5187276616</v>
       </c>
       <c r="P87">
-        <v>-22.822521774</v>
+        <v>-23.1118526184</v>
       </c>
       <c r="Q87">
-        <v>-20.642521774</v>
+        <v>-20.9318526184</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3797115076784042</v>
+        <v>0.4035623296554331</v>
       </c>
       <c r="T87">
-        <v>7.711582163473539</v>
+        <v>8.262409460864506</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01583906279079281</v>
+        <v>0.01565488764206267</v>
       </c>
       <c r="W87">
-        <v>0.232065148993931</v>
+        <v>0.2321085774940016</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.07199573995814912</v>
+        <v>0.07115858019119392</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8583,22 +8583,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.256112102796602</v>
+        <v>0.258012102796602</v>
       </c>
       <c r="C88">
-        <v>-90.63896184360557</v>
+        <v>-92.53158420639062</v>
       </c>
       <c r="D88">
-        <v>35.68763815639442</v>
+        <v>35.36811579360938</v>
       </c>
       <c r="E88">
-        <v>133.2766</v>
+        <v>134.8497</v>
       </c>
       <c r="F88">
-        <v>135.2866</v>
+        <v>136.8597</v>
       </c>
       <c r="G88">
         <v>8.960000000000001</v>
@@ -8619,37 +8619,37 @@
         <v>2.27</v>
       </c>
       <c r="M88">
-        <v>31.90058028</v>
+        <v>32.27151726</v>
       </c>
       <c r="N88">
-        <v>-29.63058028</v>
+        <v>-30.00151726</v>
       </c>
       <c r="O88">
-        <v>-6.5187276616</v>
+        <v>-6.600333797200001</v>
       </c>
       <c r="P88">
-        <v>-23.1118526184</v>
+        <v>-23.4011834628</v>
       </c>
       <c r="Q88">
-        <v>-20.9318526184</v>
+        <v>-21.2211834628</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4035623296554331</v>
+        <v>0.4310825088596971</v>
       </c>
       <c r="T88">
-        <v>8.262409460864506</v>
+        <v>8.897979419392543</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01565488764206267</v>
+        <v>0.01547494640479758</v>
       </c>
       <c r="W88">
-        <v>0.2321085774940016</v>
+        <v>0.2321510076377487</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.07115858019119392</v>
+        <v>0.07034066547635265</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8665,22 +8665,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.258012102796602</v>
+        <v>0.259912102796602</v>
       </c>
       <c r="C89">
-        <v>-92.53158420639062</v>
+        <v>-94.41853577820811</v>
       </c>
       <c r="D89">
-        <v>35.36811579360938</v>
+        <v>35.05426422179191</v>
       </c>
       <c r="E89">
-        <v>134.8497</v>
+        <v>136.4228</v>
       </c>
       <c r="F89">
-        <v>136.8597</v>
+        <v>138.4328</v>
       </c>
       <c r="G89">
         <v>8.960000000000001</v>
@@ -8701,37 +8701,37 @@
         <v>2.27</v>
       </c>
       <c r="M89">
-        <v>32.27151726</v>
+        <v>32.64245424000001</v>
       </c>
       <c r="N89">
-        <v>-30.00151726</v>
+        <v>-30.37245424000001</v>
       </c>
       <c r="O89">
-        <v>-6.600333797200001</v>
+        <v>-6.681939932800002</v>
       </c>
       <c r="P89">
-        <v>-23.4011834628</v>
+        <v>-23.6905143072</v>
       </c>
       <c r="Q89">
-        <v>-21.2211834628</v>
+        <v>-21.5105143072</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4310825088596971</v>
+        <v>0.4631893845980053</v>
       </c>
       <c r="T89">
-        <v>8.897979419392543</v>
+        <v>9.639477704341925</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01547494640479758</v>
+        <v>0.01529909474110669</v>
       </c>
       <c r="W89">
-        <v>0.2321510076377487</v>
+        <v>0.232192473460047</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.07034066547635265</v>
+        <v>0.06954133973230314</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8747,22 +8747,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.259912102796602</v>
+        <v>0.261812102796602</v>
       </c>
       <c r="C90">
-        <v>-94.41853577820811</v>
+        <v>-96.29996619654634</v>
       </c>
       <c r="D90">
-        <v>35.05426422179191</v>
+        <v>34.74593380345366</v>
       </c>
       <c r="E90">
-        <v>136.4228</v>
+        <v>137.9959</v>
       </c>
       <c r="F90">
-        <v>138.4328</v>
+        <v>140.0059</v>
       </c>
       <c r="G90">
         <v>8.960000000000001</v>
@@ -8783,37 +8783,37 @@
         <v>2.27</v>
       </c>
       <c r="M90">
-        <v>32.64245424000001</v>
+        <v>33.01339122</v>
       </c>
       <c r="N90">
-        <v>-30.37245424000001</v>
+        <v>-30.74339122</v>
       </c>
       <c r="O90">
-        <v>-6.681939932800002</v>
+        <v>-6.763546068400001</v>
       </c>
       <c r="P90">
-        <v>-23.6905143072</v>
+        <v>-23.9798451516</v>
       </c>
       <c r="Q90">
-        <v>-21.5105143072</v>
+        <v>-21.7998451516</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4631893845980053</v>
+        <v>0.5011338741069149</v>
       </c>
       <c r="T90">
-        <v>9.639477704341925</v>
+        <v>10.5157938592821</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01529909474110669</v>
+        <v>0.01512719480019539</v>
       </c>
       <c r="W90">
-        <v>0.232192473460047</v>
+        <v>0.2322330074661139</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06954133973230314</v>
+        <v>0.06875997636452447</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8829,22 +8829,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.261812102796602</v>
+        <v>0.2637121027966021</v>
       </c>
       <c r="C91">
-        <v>-96.29996619654634</v>
+        <v>-98.17601988006977</v>
       </c>
       <c r="D91">
-        <v>34.74593380345366</v>
+        <v>34.44298011993023</v>
       </c>
       <c r="E91">
-        <v>137.9959</v>
+        <v>139.569</v>
       </c>
       <c r="F91">
-        <v>140.0059</v>
+        <v>141.579</v>
       </c>
       <c r="G91">
         <v>8.960000000000001</v>
@@ -8865,37 +8865,37 @@
         <v>2.27</v>
       </c>
       <c r="M91">
-        <v>33.01339122</v>
+        <v>33.38432820000001</v>
       </c>
       <c r="N91">
-        <v>-30.74339122</v>
+        <v>-31.11432820000001</v>
       </c>
       <c r="O91">
-        <v>-6.763546068400001</v>
+        <v>-6.845152204000001</v>
       </c>
       <c r="P91">
-        <v>-23.9798451516</v>
+        <v>-24.269175996</v>
       </c>
       <c r="Q91">
-        <v>-21.7998451516</v>
+        <v>-22.08917599600001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5011338741069149</v>
+        <v>0.5466672615176065</v>
       </c>
       <c r="T91">
-        <v>10.5157938592821</v>
+        <v>11.56737324521031</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01512719480019539</v>
+        <v>0.01495911485797099</v>
       </c>
       <c r="W91">
-        <v>0.2322330074661139</v>
+        <v>0.2322726407164905</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06875997636452447</v>
+        <v>0.06799597662714085</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8911,22 +8911,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2637121027966021</v>
+        <v>0.265612102796602</v>
       </c>
       <c r="C92">
-        <v>-98.17601988006977</v>
+        <v>-100.0468362541696</v>
       </c>
       <c r="D92">
-        <v>34.44298011993023</v>
+        <v>34.14526374583039</v>
       </c>
       <c r="E92">
-        <v>139.569</v>
+        <v>141.1421</v>
       </c>
       <c r="F92">
-        <v>141.579</v>
+        <v>143.1521</v>
       </c>
       <c r="G92">
         <v>8.960000000000001</v>
@@ -8947,37 +8947,37 @@
         <v>2.27</v>
       </c>
       <c r="M92">
-        <v>33.38432820000001</v>
+        <v>33.75526518000001</v>
       </c>
       <c r="N92">
-        <v>-31.11432820000001</v>
+        <v>-31.48526518000001</v>
       </c>
       <c r="O92">
-        <v>-6.845152204000001</v>
+        <v>-6.926758339600002</v>
       </c>
       <c r="P92">
-        <v>-24.269175996</v>
+        <v>-24.55850684040001</v>
       </c>
       <c r="Q92">
-        <v>-22.08917599600001</v>
+        <v>-22.37850684040001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5466672615176065</v>
+        <v>0.6023191794640073</v>
       </c>
       <c r="T92">
-        <v>11.56737324521031</v>
+        <v>12.85263693912257</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01495911485797099</v>
+        <v>0.01479472898041087</v>
       </c>
       <c r="W92">
-        <v>0.2322726407164905</v>
+        <v>0.2323114029064191</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06799597662714085</v>
+        <v>0.06724876809277669</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8993,22 +8993,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.265612102796602</v>
+        <v>0.267512102796602</v>
       </c>
       <c r="C93">
-        <v>-100.0468362541696</v>
+        <v>-101.9125499649177</v>
       </c>
       <c r="D93">
-        <v>34.14526374583039</v>
+        <v>33.8526500350823</v>
       </c>
       <c r="E93">
-        <v>141.1421</v>
+        <v>142.7152</v>
       </c>
       <c r="F93">
-        <v>143.1521</v>
+        <v>144.7252</v>
       </c>
       <c r="G93">
         <v>8.960000000000001</v>
@@ -9029,37 +9029,37 @@
         <v>2.27</v>
       </c>
       <c r="M93">
-        <v>33.75526518000001</v>
+        <v>34.12620216</v>
       </c>
       <c r="N93">
-        <v>-31.48526518000001</v>
+        <v>-31.85620216</v>
       </c>
       <c r="O93">
-        <v>-6.926758339600002</v>
+        <v>-7.0083644752</v>
       </c>
       <c r="P93">
-        <v>-24.55850684040001</v>
+        <v>-24.8478376848</v>
       </c>
       <c r="Q93">
-        <v>-22.37850684040001</v>
+        <v>-22.6678376848</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6023191794640073</v>
+        <v>0.6718840768970082</v>
       </c>
       <c r="T93">
-        <v>12.85263693912257</v>
+        <v>14.45921655651289</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01479472898041087</v>
+        <v>0.01463391670888467</v>
       </c>
       <c r="W93">
-        <v>0.2323114029064191</v>
+        <v>0.232349322440045</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06724876809277669</v>
+        <v>0.06651780322220302</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9075,22 +9075,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.267512102796602</v>
+        <v>0.269412102796602</v>
       </c>
       <c r="C94">
-        <v>-101.9125499649177</v>
+        <v>-103.7732910821124</v>
       </c>
       <c r="D94">
-        <v>33.8526500350823</v>
+        <v>33.56500891788765</v>
       </c>
       <c r="E94">
-        <v>142.7152</v>
+        <v>144.2883</v>
       </c>
       <c r="F94">
-        <v>144.7252</v>
+        <v>146.2983</v>
       </c>
       <c r="G94">
         <v>8.960000000000001</v>
@@ -9111,37 +9111,37 @@
         <v>2.27</v>
       </c>
       <c r="M94">
-        <v>34.12620216</v>
+        <v>34.49713914</v>
       </c>
       <c r="N94">
-        <v>-31.85620216</v>
+        <v>-32.22713914</v>
       </c>
       <c r="O94">
-        <v>-7.0083644752</v>
+        <v>-7.0899706108</v>
       </c>
       <c r="P94">
-        <v>-24.8478376848</v>
+        <v>-25.1371685292</v>
       </c>
       <c r="Q94">
-        <v>-22.6678376848</v>
+        <v>-22.9571685292</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6718840768970082</v>
+        <v>0.7613246593108667</v>
       </c>
       <c r="T94">
-        <v>14.45921655651289</v>
+        <v>16.52481892172903</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01463391670888467</v>
+        <v>0.01447656276577838</v>
       </c>
       <c r="W94">
-        <v>0.232349322440045</v>
+        <v>0.2323864264998295</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06651780322220302</v>
+        <v>0.06580255802626545</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9157,22 +9157,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.269412102796602</v>
+        <v>0.2713121027966021</v>
       </c>
       <c r="C95">
-        <v>-103.7732910821124</v>
+        <v>-105.62918529206</v>
       </c>
       <c r="D95">
-        <v>33.56500891788765</v>
+        <v>33.28221470794005</v>
       </c>
       <c r="E95">
-        <v>144.2883</v>
+        <v>145.8614</v>
       </c>
       <c r="F95">
-        <v>146.2983</v>
+        <v>147.8714</v>
       </c>
       <c r="G95">
         <v>8.960000000000001</v>
@@ -9193,37 +9193,37 @@
         <v>2.27</v>
       </c>
       <c r="M95">
-        <v>34.49713914</v>
+        <v>34.86807612</v>
       </c>
       <c r="N95">
-        <v>-32.22713914</v>
+        <v>-32.59807612</v>
       </c>
       <c r="O95">
-        <v>-7.0899706108</v>
+        <v>-7.1715767464</v>
       </c>
       <c r="P95">
-        <v>-25.1371685292</v>
+        <v>-25.4264993736</v>
       </c>
       <c r="Q95">
-        <v>-22.9571685292</v>
+        <v>-23.2464993736</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7613246593108667</v>
+        <v>0.8805787691960114</v>
       </c>
       <c r="T95">
-        <v>16.52481892172903</v>
+        <v>19.27895540868387</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01447656276577838</v>
+        <v>0.0143225567789084</v>
       </c>
       <c r="W95">
-        <v>0.2323864264998295</v>
+        <v>0.2324227411115334</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06580255802626545</v>
+        <v>0.06510253081322004</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9239,22 +9239,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2713121027966021</v>
+        <v>0.2732121027966021</v>
       </c>
       <c r="C96">
-        <v>-105.62918529206</v>
+        <v>-107.4803540806927</v>
       </c>
       <c r="D96">
-        <v>33.28221470794005</v>
+        <v>33.00414591930726</v>
       </c>
       <c r="E96">
-        <v>145.8614</v>
+        <v>147.4345</v>
       </c>
       <c r="F96">
-        <v>147.8714</v>
+        <v>149.4445</v>
       </c>
       <c r="G96">
         <v>8.960000000000001</v>
@@ -9275,37 +9275,37 @@
         <v>2.27</v>
       </c>
       <c r="M96">
-        <v>34.86807612</v>
+        <v>35.2390131</v>
       </c>
       <c r="N96">
-        <v>-32.59807612</v>
+        <v>-32.9690131</v>
       </c>
       <c r="O96">
-        <v>-7.1715767464</v>
+        <v>-7.253182882</v>
       </c>
       <c r="P96">
-        <v>-25.4264993736</v>
+        <v>-25.715830218</v>
       </c>
       <c r="Q96">
-        <v>-23.2464993736</v>
+        <v>-23.535830218</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8805787691960114</v>
+        <v>1.047534523035214</v>
       </c>
       <c r="T96">
-        <v>19.27895540868387</v>
+        <v>23.13474649042065</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0143225567789084</v>
+        <v>0.01417179302334094</v>
       </c>
       <c r="W96">
-        <v>0.2324227411115334</v>
+        <v>0.2324582912050962</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06510253081322004</v>
+        <v>0.0644172410151862</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9321,22 +9321,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2732121027966021</v>
+        <v>0.275112102796602</v>
       </c>
       <c r="C97">
-        <v>-107.4803540806927</v>
+        <v>-109.3269149075829</v>
       </c>
       <c r="D97">
-        <v>33.00414591930726</v>
+        <v>32.7306850924171</v>
       </c>
       <c r="E97">
-        <v>147.4345</v>
+        <v>149.0076</v>
       </c>
       <c r="F97">
-        <v>149.4445</v>
+        <v>151.0176</v>
       </c>
       <c r="G97">
         <v>8.960000000000001</v>
@@ -9357,37 +9357,37 @@
         <v>2.27</v>
       </c>
       <c r="M97">
-        <v>35.2390131</v>
+        <v>35.60995008</v>
       </c>
       <c r="N97">
-        <v>-32.9690131</v>
+        <v>-33.33995008</v>
       </c>
       <c r="O97">
-        <v>-7.253182882</v>
+        <v>-7.3347890176</v>
       </c>
       <c r="P97">
-        <v>-25.715830218</v>
+        <v>-26.0051610624</v>
       </c>
       <c r="Q97">
-        <v>-23.535830218</v>
+        <v>-23.8251610624</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.047534523035214</v>
+        <v>1.297968153794018</v>
       </c>
       <c r="T97">
-        <v>23.13474649042065</v>
+        <v>28.91843311302582</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01417179302334094</v>
+        <v>0.0140241701793478</v>
       </c>
       <c r="W97">
-        <v>0.2324582912050962</v>
+        <v>0.2324931006717098</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0644172410151862</v>
+        <v>0.06374622808794461</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9403,22 +9403,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.275112102796602</v>
+        <v>0.277012102796602</v>
       </c>
       <c r="C98">
-        <v>-109.3269149075829</v>
+        <v>-111.168981371377</v>
       </c>
       <c r="D98">
-        <v>32.7306850924171</v>
+        <v>32.46171862862303</v>
       </c>
       <c r="E98">
-        <v>149.0076</v>
+        <v>150.5807</v>
       </c>
       <c r="F98">
-        <v>151.0176</v>
+        <v>152.5907</v>
       </c>
       <c r="G98">
         <v>8.960000000000001</v>
@@ -9439,37 +9439,37 @@
         <v>2.27</v>
       </c>
       <c r="M98">
-        <v>35.60995008</v>
+        <v>35.98088706</v>
       </c>
       <c r="N98">
-        <v>-33.33995007999999</v>
+        <v>-33.71088706</v>
       </c>
       <c r="O98">
-        <v>-7.334789017599999</v>
+        <v>-7.4163951532</v>
       </c>
       <c r="P98">
-        <v>-26.0051610624</v>
+        <v>-26.2944919068</v>
       </c>
       <c r="Q98">
-        <v>-23.8251610624</v>
+        <v>-24.1144919068</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.297968153794015</v>
+        <v>1.71535753839202</v>
       </c>
       <c r="T98">
-        <v>28.91843311302575</v>
+        <v>38.55791081736767</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0140241701793478</v>
+        <v>0.01387959110533391</v>
       </c>
       <c r="W98">
-        <v>0.2324931006717098</v>
+        <v>0.2325271924173623</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06374622808794461</v>
+        <v>0.06308905047879054</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9485,22 +9485,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.277012102796602</v>
+        <v>0.2789121027966021</v>
       </c>
       <c r="C99">
-        <v>-111.168981371377</v>
+        <v>-113.0066633671398</v>
       </c>
       <c r="D99">
-        <v>32.46171862862303</v>
+        <v>32.19713663286024</v>
       </c>
       <c r="E99">
-        <v>150.5807</v>
+        <v>152.1538</v>
       </c>
       <c r="F99">
-        <v>152.5907</v>
+        <v>154.1638</v>
       </c>
       <c r="G99">
         <v>8.960000000000001</v>
@@ -9521,37 +9521,37 @@
         <v>2.27</v>
       </c>
       <c r="M99">
-        <v>35.98088706</v>
+        <v>36.35182404</v>
       </c>
       <c r="N99">
-        <v>-33.71088706</v>
+        <v>-34.08182404</v>
       </c>
       <c r="O99">
-        <v>-7.4163951532</v>
+        <v>-7.4980012888</v>
       </c>
       <c r="P99">
-        <v>-26.2944919068</v>
+        <v>-26.5838227512</v>
       </c>
       <c r="Q99">
-        <v>-24.1144919068</v>
+        <v>-24.4038227512</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.71535753839202</v>
+        <v>2.550136307588029</v>
       </c>
       <c r="T99">
-        <v>38.55791081736767</v>
+        <v>57.8368662260515</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01387959110533391</v>
+        <v>0.01373796262466724</v>
       </c>
       <c r="W99">
-        <v>0.2325271924173623</v>
+        <v>0.2325605884131035</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.06308905047879054</v>
+        <v>0.06244528465757848</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9567,22 +9567,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2789121027966021</v>
+        <v>0.280812102796602</v>
       </c>
       <c r="C100">
-        <v>-113.0066633671398</v>
+        <v>-114.8400672360659</v>
       </c>
       <c r="D100">
-        <v>32.19713663286024</v>
+        <v>31.93683276393406</v>
       </c>
       <c r="E100">
-        <v>152.1538</v>
+        <v>153.7269</v>
       </c>
       <c r="F100">
-        <v>154.1638</v>
+        <v>155.7369</v>
       </c>
       <c r="G100">
         <v>8.960000000000001</v>
@@ -9603,37 +9603,37 @@
         <v>2.27</v>
       </c>
       <c r="M100">
-        <v>36.35182404</v>
+        <v>36.72276102</v>
       </c>
       <c r="N100">
-        <v>-34.08182404</v>
+        <v>-34.45276102</v>
       </c>
       <c r="O100">
-        <v>-7.4980012888</v>
+        <v>-7.5796074244</v>
       </c>
       <c r="P100">
-        <v>-26.5838227512</v>
+        <v>-26.8731535956</v>
       </c>
       <c r="Q100">
-        <v>-24.4038227512</v>
+        <v>-24.6931535956</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.550136307588029</v>
+        <v>5.054472615176059</v>
       </c>
       <c r="T100">
-        <v>57.8368662260515</v>
+        <v>115.673732452103</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01373796262466724</v>
+        <v>0.01359919532542818</v>
       </c>
       <c r="W100">
-        <v>0.2325605884131035</v>
+        <v>0.2325933097422641</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9641,91 +9641,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.06244528465757848</v>
+        <v>0.06181452420649181</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.280812102796602</v>
-      </c>
-      <c r="C101">
-        <v>-114.8400672360659</v>
-      </c>
-      <c r="D101">
-        <v>31.93683276393406</v>
-      </c>
-      <c r="E101">
-        <v>153.7269</v>
-      </c>
-      <c r="F101">
-        <v>155.7369</v>
-      </c>
-      <c r="G101">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="H101">
-        <v>155.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.45</v>
-      </c>
-      <c r="K101">
-        <v>2.18</v>
-      </c>
-      <c r="L101">
-        <v>2.27</v>
-      </c>
-      <c r="M101">
-        <v>36.72276102</v>
-      </c>
-      <c r="N101">
-        <v>-34.45276102</v>
-      </c>
-      <c r="O101">
-        <v>-7.5796074244</v>
-      </c>
-      <c r="P101">
-        <v>-26.8731535956</v>
-      </c>
-      <c r="Q101">
-        <v>-24.6931535956</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.054472615176059</v>
-      </c>
-      <c r="T101">
-        <v>115.673732452103</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01359919532542818</v>
-      </c>
-      <c r="W101">
-        <v>0.2325933097422641</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.06181452420649181</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
